--- a/generated/spreadsheet/verbose/removal-or-variation-of-a-condition-following-grant-of-planning-permission-s73-verbose.xlsx
+++ b/generated/spreadsheet/verbose/removal-or-variation-of-a-condition-following-grant-of-planning-permission-s73-verbose.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N91"/>
+  <dimension ref="A1:N90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
@@ -435,8 +435,8 @@
     <col width="72" customWidth="1" min="3" max="3"/>
     <col width="28" customWidth="1" min="4" max="4"/>
     <col width="31" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
     <col width="18" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
@@ -642,12 +642,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>application-sub-type</t>
+          <t>planning-authority</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Application sub type</t>
+          <t>Planning authority</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr"/>
@@ -656,7 +656,7 @@
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>Further classification of the application type for specific variations within the main application type</t>
+          <t>A reference of the planning authority the application has been submitted to, e.g. local-authority:CMD for London borough of Camden</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -666,7 +666,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -690,12 +690,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>planning-authority</t>
+          <t>submission-date</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Planning authority</t>
+          <t>Submission date</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr"/>
@@ -704,12 +704,12 @@
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>A reference of the planning authority the application has been submitted to, e.g. local-authority:CMD for London borough of Camden</t>
+          <t>Date the application is submitted in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -738,12 +738,12 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>submission-date</t>
+          <t>modules</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Submission date</t>
+          <t>Modules[]</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr"/>
@@ -752,12 +752,12 @@
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>Date the application is submitted in YYYY-MM-DD format</t>
+          <t>List of required modules for this application that can be used to validate the application</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -786,21 +786,29 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>modules</t>
+          <t>documents</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Modules[]</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr"/>
-      <c r="I7" s="2" t="inlineStr"/>
+          <t>Documents[]</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>List of required modules for this application that can be used to validate the application</t>
+          <t>Unique reference for the document within this application submission, generated by the submitting system</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -844,19 +852,19 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>reference</t>
+          <t>name</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>Unique reference for the document within this application submission, generated by the submitting system</t>
+          <t>The name or title of the document</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -900,19 +908,19 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>description</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>The name or title of the document</t>
+          <t>Brief description of what the document contains</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -922,7 +930,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -956,29 +964,29 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>document-types</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Document types[]</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>Brief description of what the document contains</t>
+          <t>List of codelist references that the document covers</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1012,24 +1020,24 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>document-types</t>
+          <t>uploaded-date</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>Document types[]</t>
+          <t>Uploaded date</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>List of codelist references that the document covers</t>
+          <t>The date the document was uploaded to the application</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1068,29 +1076,37 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>uploaded-date</t>
+          <t>file</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>Uploaded date</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr"/>
-      <c r="K12" s="2" t="inlineStr"/>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>base64-content</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>Base64</t>
+        </is>
+      </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>The date the document was uploaded to the application</t>
+          <t>Base64-encoded content of the file for inline file uploads</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1134,17 +1150,17 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>base64-content</t>
+          <t>filename</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>Base64</t>
+          <t>Filename</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>Base64-encoded content of the file for inline file uploads</t>
+          <t>Name of the file being uploaded</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -1154,7 +1170,7 @@
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1198,17 +1214,17 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>filename</t>
+          <t>mime-type</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>Filename</t>
+          <t>MIME type</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>Name of the file being uploaded</t>
+          <t>The file's MIME type such as application/pdf or image/jpeg</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1218,7 +1234,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1262,22 +1278,22 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>mime-type</t>
+          <t>file-size</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>MIME type</t>
+          <t>File size</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>The file's MIME type such as application/pdf or image/jpeg</t>
+          <t>Size of the file in bytes that can be used to enforce limits</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>number</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1306,37 +1322,29 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>documents</t>
+          <t>fee</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Documents[]</t>
+          <t>Fee</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>file</t>
+          <t>amount</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>File</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>file-size</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>File size</t>
-        </is>
-      </c>
+          <t>Amount</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>Size of the file in bytes that can be used to enforce limits</t>
+          <t>The total amount due for the application fee</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
@@ -1346,7 +1354,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1380,19 +1388,19 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>amount</t>
+          <t>amount-paid</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>Amount</t>
+          <t>Amount paid</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr"/>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>The total amount due for the application fee</t>
+          <t>The amount paid towards the application fee</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -1436,75 +1444,67 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>amount-paid</t>
+          <t>transactions</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>Amount paid</t>
+          <t>Transactions[]</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>The amount paid towards the application fee</t>
+          <t>References to payments or financial transactions related to this application</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="n"/>
-      <c r="B19" s="2" t="n"/>
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Agent contact details</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>agent-contact</t>
+        </is>
+      </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Name and contact information if an agent is being used.</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>agent-reference</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>fee</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>Fee</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>transactions</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>Transactions[]</t>
-        </is>
-      </c>
+          <t>Agent reference</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr"/>
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr"/>
+      <c r="I19" s="2" t="inlineStr"/>
       <c r="J19" s="2" t="inlineStr"/>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>References to payments or financial transactions related to this application</t>
+          <t>A reference to an agent object</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
@@ -1514,21 +1514,13 @@
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>Agent contact details</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>agent-contact</t>
-        </is>
-      </c>
+      <c r="A20" s="2" t="n"/>
+      <c r="B20" s="2" t="n"/>
       <c r="C20" s="2" t="inlineStr">
         <is>
           <t>Name and contact information if an agent is being used.</t>
@@ -1536,23 +1528,31 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>agent-reference</t>
+          <t>contact-details</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Agent reference</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr"/>
-      <c r="G20" s="2" t="inlineStr"/>
+          <t>Contact details</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
       <c r="H20" s="2" t="inlineStr"/>
       <c r="I20" s="2" t="inlineStr"/>
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>A reference to an agent object</t>
+          <t>The email address that can be used for electronic correspondence with the individual</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -1586,21 +1586,29 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>phone-numbers</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr"/>
-      <c r="I21" s="2" t="inlineStr"/>
+          <t>Phone number(s)[]</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>Phone number</t>
+        </is>
+      </c>
       <c r="J21" s="2" t="inlineStr"/>
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>The email address that can be used for electronic correspondence with the individual</t>
+          <t>A phone number</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
@@ -1610,7 +1618,7 @@
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1644,24 +1652,24 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>contact-priority</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>Phone number</t>
+          <t>Contact priority</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr"/>
       <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>The priority of a number</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -1671,8 +1679,16 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="n"/>
-      <c r="B23" s="2" t="n"/>
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Agent details</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>agent-details</t>
+        </is>
+      </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
           <t>Name and contact information if an agent is being used.</t>
@@ -1680,63 +1696,47 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>contact-details</t>
+          <t>agent</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Contact details</t>
+          <t>agent</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>phone-numbers</t>
+          <t>reference</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>Phone number(s)[]</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>contact-priority</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>Contact priority</t>
-        </is>
-      </c>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr"/>
+      <c r="I23" s="2" t="inlineStr"/>
       <c r="J23" s="2" t="inlineStr"/>
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>The priority of a number</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>Agent details</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>agent-details</t>
-        </is>
-      </c>
+      <c r="A24" s="2" t="n"/>
+      <c r="B24" s="2" t="n"/>
       <c r="C24" s="2" t="inlineStr">
         <is>
           <t>Name and contact information if an agent is being used.</t>
@@ -1754,21 +1754,29 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>reference</t>
+          <t>person</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr"/>
-      <c r="I24" s="2" t="inlineStr"/>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>The title of the individual</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
@@ -1778,7 +1786,7 @@
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1812,19 +1820,19 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>title</t>
+          <t>first-name</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr"/>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>The title of the individual</t>
+          <t>The first name of the individual</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
@@ -1834,7 +1842,7 @@
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1868,19 +1876,19 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>first-name</t>
+          <t>last-name</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>First Name</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr"/>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>The first name of the individual</t>
+          <t>The last name of the individual</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -1924,19 +1932,19 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>last-name</t>
+          <t>address-text</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>Address Text</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr"/>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>The last name of the individual</t>
+          <t>Flexible field for capturing addresses</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
@@ -1980,19 +1988,19 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>address-text</t>
+          <t>postcode</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Postcode</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The postal code</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
@@ -2002,7 +2010,7 @@
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2026,29 +2034,21 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>person</t>
+          <t>company</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>postcode</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>Postcode</t>
-        </is>
-      </c>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr"/>
+      <c r="I29" s="2" t="inlineStr"/>
       <c r="J29" s="2" t="inlineStr"/>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>The name of a company (that the agent works for)</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
@@ -2082,12 +2082,12 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>company</t>
+          <t>user-role</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Company</t>
+          <t>User role</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr"/>
@@ -2096,12 +2096,12 @@
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>The name of a company (that the agent works for)</t>
+          <t>The role of the named individual. Agent or proxy</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -2111,64 +2111,56 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="n"/>
-      <c r="B31" s="2" t="n"/>
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>Applicant contact details</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>applicant-contact</t>
+        </is>
+      </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Name and contact information if an agent is being used.</t>
+          <t>Telephone number and email address of the applicant.</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>agent</t>
+          <t>applicant-reference</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>agent</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>user-role</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>User role</t>
-        </is>
-      </c>
+          <t>Applicant reference</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr"/>
+      <c r="G31" s="2" t="inlineStr"/>
       <c r="H31" s="2" t="inlineStr"/>
       <c r="I31" s="2" t="inlineStr"/>
       <c r="J31" s="2" t="inlineStr"/>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>The role of the named individual. Agent or proxy</t>
+          <t>Reference to match contact details to a named individual from the applicant details component</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>Applicant contact details</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>applicant-contact</t>
-        </is>
-      </c>
+      <c r="A32" s="2" t="n"/>
+      <c r="B32" s="2" t="n"/>
       <c r="C32" s="2" t="inlineStr">
         <is>
           <t>Telephone number and email address of the applicant.</t>
@@ -2176,23 +2168,31 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>applicant-reference</t>
+          <t>contact-details</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Applicant reference</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr"/>
-      <c r="G32" s="2" t="inlineStr"/>
+          <t>Contact details</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
       <c r="H32" s="2" t="inlineStr"/>
       <c r="I32" s="2" t="inlineStr"/>
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>Reference to match contact details to a named individual from the applicant details component</t>
+          <t>The email address that can be used for electronic correspondence with the individual</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
@@ -2226,21 +2226,29 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>phone-numbers</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr"/>
-      <c r="I33" s="2" t="inlineStr"/>
+          <t>Phone number(s)[]</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>Phone number</t>
+        </is>
+      </c>
       <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>The email address that can be used for electronic correspondence with the individual</t>
+          <t>A phone number</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
@@ -2250,7 +2258,7 @@
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2284,24 +2292,24 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>contact-priority</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>Phone number</t>
+          <t>Contact priority</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>The priority of a number</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -2311,72 +2319,64 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="n"/>
-      <c r="B35" s="2" t="n"/>
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>Applicant details</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>applicant-details</t>
+        </is>
+      </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Telephone number and email address of the applicant.</t>
+          <t>Name and contact information for the parties making the application.</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>contact-details</t>
+          <t>applicants</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Contact details</t>
+          <t>Applicants[]</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>phone-numbers</t>
+          <t>reference</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>Phone number(s)[]</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>contact-priority</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>Contact priority</t>
-        </is>
-      </c>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr"/>
+      <c r="I35" s="2" t="inlineStr"/>
       <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>The priority of a number</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>Applicant details</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>applicant-details</t>
-        </is>
-      </c>
+      <c r="A36" s="2" t="n"/>
+      <c r="B36" s="2" t="n"/>
       <c r="C36" s="2" t="inlineStr">
         <is>
           <t>Name and contact information for the parties making the application.</t>
@@ -2394,21 +2394,29 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>reference</t>
+          <t>person</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr"/>
-      <c r="I36" s="2" t="inlineStr"/>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>The title of the individual</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
@@ -2418,7 +2426,7 @@
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2452,19 +2460,19 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>title</t>
+          <t>first-name</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr"/>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>The title of the individual</t>
+          <t>The first name of the individual</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
@@ -2474,7 +2482,7 @@
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2508,19 +2516,19 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>first-name</t>
+          <t>last-name</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>First Name</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>The first name of the individual</t>
+          <t>The last name of the individual</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
@@ -2564,19 +2572,19 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>last-name</t>
+          <t>address-text</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>Address Text</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>The last name of the individual</t>
+          <t>Flexible field for capturing addresses</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
@@ -2620,19 +2628,19 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>address-text</t>
+          <t>postcode</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Postcode</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The postal code</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
@@ -2642,53 +2650,45 @@
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="n"/>
-      <c r="B41" s="2" t="n"/>
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>Checklist</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>checklist</t>
+        </is>
+      </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Name and contact information for the parties making the application.</t>
+          <t>Checking whether all the requirements of the form have been met, such as proof of payment or supporting documentation.</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>applicants</t>
+          <t>national-req-types</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>Applicants[]</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>person</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>postcode</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>Postcode</t>
-        </is>
-      </c>
+          <t>National requirement types[]</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr"/>
+      <c r="G41" s="2" t="inlineStr"/>
+      <c r="H41" s="2" t="inlineStr"/>
+      <c r="I41" s="2" t="inlineStr"/>
       <c r="J41" s="2" t="inlineStr"/>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>List of the document types required for the given application type</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
@@ -2698,97 +2698,89 @@
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Checklist</t>
+          <t>Conflict of interest</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>checklist</t>
+          <t>conflict-of-interest</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Checking whether all the requirements of the form have been met, such as proof of payment or supporting documentation.</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>national-req-types</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>National requirement types[]</t>
-        </is>
-      </c>
+          <t>Details of any conflict of interest that may exist between the applicant and planning authority.</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr"/>
+      <c r="E42" s="2" t="inlineStr"/>
       <c r="F42" s="2" t="inlineStr"/>
       <c r="G42" s="2" t="inlineStr"/>
       <c r="H42" s="2" t="inlineStr"/>
       <c r="I42" s="2" t="inlineStr"/>
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr"/>
-      <c r="L42" s="2" t="inlineStr">
-        <is>
-          <t>List of the document types required for the given application type</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="N42" s="2" t="inlineStr">
-        <is>
-          <t>MUST</t>
-        </is>
-      </c>
+      <c r="L42" s="2" t="inlineStr"/>
+      <c r="M42" s="2" t="inlineStr"/>
+      <c r="N42" s="2" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>Conflict of interest</t>
+          <t>Condition removal or variation</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>conflict-of-interest</t>
+          <t>con-remove-vary</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Details of any conflict of interest that may exist between the applicant and planning authority.</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr"/>
-      <c r="E43" s="2" t="inlineStr"/>
+          <t>Why the applicant is asking for planning conditions to be removed or changed.</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>reason</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>Reason</t>
+        </is>
+      </c>
       <c r="F43" s="2" t="inlineStr"/>
       <c r="G43" s="2" t="inlineStr"/>
       <c r="H43" s="2" t="inlineStr"/>
       <c r="I43" s="2" t="inlineStr"/>
       <c r="J43" s="2" t="inlineStr"/>
       <c r="K43" s="2" t="inlineStr"/>
-      <c r="L43" s="2" t="inlineStr"/>
-      <c r="M43" s="2" t="inlineStr"/>
-      <c r="N43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>The reason why the applicant wishes condition(s) to be removed or changed</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>Condition removal or variation</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>con-remove-vary</t>
-        </is>
-      </c>
+      <c r="A44" s="2" t="n"/>
+      <c r="B44" s="2" t="n"/>
       <c r="C44" s="2" t="inlineStr">
         <is>
           <t>Why the applicant is asking for planning conditions to be removed or changed.</t>
@@ -2796,12 +2788,12 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>reason</t>
+          <t>condition-change</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Reason</t>
+          <t>Condition change</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr"/>
@@ -2812,7 +2804,7 @@
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>The reason why the applicant wishes condition(s) to be removed or changed</t>
+          <t>State how the condition should vary</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
@@ -2822,26 +2814,34 @@
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="n"/>
-      <c r="B45" s="2" t="n"/>
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>Declaration</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>declaration</t>
+        </is>
+      </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Why the applicant is asking for planning conditions to be removed or changed.</t>
+          <t>Signed and dated verification of the application's accuracy.</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>condition-change</t>
+          <t>name</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>Condition change</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr"/>
@@ -2852,7 +2852,7 @@
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>State how the condition should vary</t>
+          <t>A name of a person</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
@@ -2862,21 +2862,13 @@
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>Declaration</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>declaration</t>
-        </is>
-      </c>
+      <c r="A46" s="2" t="n"/>
+      <c r="B46" s="2" t="n"/>
       <c r="C46" s="2" t="inlineStr">
         <is>
           <t>Signed and dated verification of the application's accuracy.</t>
@@ -2884,12 +2876,12 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>declaration-confirmed</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Declaration confirmed</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr"/>
@@ -2900,12 +2892,12 @@
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>A name of a person</t>
+          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -2924,12 +2916,12 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>declaration-confirmed</t>
+          <t>declaration-date</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>Declaration confirmed</t>
+          <t>Declaration date</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr"/>
@@ -2940,12 +2932,12 @@
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
+          <t>The date the declaration was made</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -2955,32 +2947,48 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="n"/>
-      <c r="B48" s="2" t="n"/>
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>Description of your proposal</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>desc-your-proposal</t>
+        </is>
+      </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Signed and dated verification of the application's accuracy.</t>
+          <t>Written description of the proposed development including any additional relevant details.</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>declaration-date</t>
+          <t>related-application</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Declaration date</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="inlineStr"/>
-      <c r="G48" s="2" t="inlineStr"/>
+          <t>Related application</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
       <c r="H48" s="2" t="inlineStr"/>
       <c r="I48" s="2" t="inlineStr"/>
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>The date the declaration was made</t>
+          <t>The reference for the related application</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
@@ -2995,16 +3003,8 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>Description of your proposal</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>desc-your-proposal</t>
-        </is>
-      </c>
+      <c r="A49" s="2" t="n"/>
+      <c r="B49" s="2" t="n"/>
       <c r="C49" s="2" t="inlineStr">
         <is>
           <t>Written description of the proposed development including any additional relevant details.</t>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>reference</t>
+          <t>description</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr"/>
@@ -3036,7 +3036,7 @@
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>The reference for the related application</t>
+          <t>A description of the related application</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
@@ -3070,12 +3070,12 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>decision-date</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Decision date</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr"/>
@@ -3084,7 +3084,7 @@
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>A description of the related application</t>
+          <t>The date when the decision was made, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
@@ -3094,7 +3094,7 @@
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3108,36 +3108,28 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>related-application</t>
+          <t>condition-numbers</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>Related application</t>
-        </is>
-      </c>
-      <c r="F51" s="2" t="inlineStr">
-        <is>
-          <t>decision-date</t>
-        </is>
-      </c>
-      <c r="G51" s="2" t="inlineStr">
-        <is>
-          <t>Decision date</t>
-        </is>
-      </c>
+          <t>Condition numbers[]</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr"/>
+      <c r="G51" s="2" t="inlineStr"/>
       <c r="H51" s="2" t="inlineStr"/>
       <c r="I51" s="2" t="inlineStr"/>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>The date when the decision was made, in YYYY-MM-DD format</t>
+          <t>List of condition numbers related to this application</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -3156,12 +3148,12 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>condition-numbers</t>
+          <t>has-development-started</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Condition numbers[]</t>
+          <t>Has development started</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr"/>
@@ -3172,17 +3164,17 @@
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>List of condition numbers related to this application</t>
+          <t>Whether the development has already started</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3196,12 +3188,12 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>has-development-started</t>
+          <t>development-start-date</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>Has development started</t>
+          <t>Development start date</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr"/>
@@ -3212,17 +3204,17 @@
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>Whether the development has already started</t>
+          <t>Date when development started</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3236,12 +3228,12 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>development-start-date</t>
+          <t>has-development-completed</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Development start date</t>
+          <t>Has development completed</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr"/>
@@ -3252,17 +3244,17 @@
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>Date when development started</t>
+          <t>Whether the development has been completed</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3276,12 +3268,12 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>has-development-completed</t>
+          <t>development-completed-date</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>Has development completed</t>
+          <t>Development completed date</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr"/>
@@ -3292,36 +3284,44 @@
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>Whether the development has been completed</t>
+          <t>Date when development was completed</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="n"/>
-      <c r="B56" s="2" t="n"/>
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>Ownership certificates and agricultural land declaration</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>ownership-certs</t>
+        </is>
+      </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Written description of the proposed development including any additional relevant details.</t>
+          <t>Who will be affected by the proposal and whether they have been notified, such as agricultural tenants</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>development-completed-date</t>
+          <t>sole-owner</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Development completed date</t>
+          <t>Sole owner</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr"/>
@@ -3332,31 +3332,23 @@
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>Date when development was completed</t>
+          <t>Is the applicant the sole owner of the land?</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>Ownership certificates and agricultural land declaration</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>ownership-certs</t>
-        </is>
-      </c>
+      <c r="A57" s="2" t="n"/>
+      <c r="B57" s="2" t="n"/>
       <c r="C57" s="2" t="inlineStr">
         <is>
           <t>Who will be affected by the proposal and whether they have been notified, such as agricultural tenants</t>
@@ -3364,12 +3356,12 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>sole-owner</t>
+          <t>agricultural-tenants</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>Sole owner</t>
+          <t>Agricultural tenants</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr"/>
@@ -3380,7 +3372,7 @@
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>Is the applicant the sole owner of the land?</t>
+          <t>Are there any agricultural tenants on the land?</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
@@ -3404,33 +3396,49 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>agricultural-tenants</t>
+          <t>owners-and-tenants</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Agricultural tenants</t>
-        </is>
-      </c>
-      <c r="F58" s="2" t="inlineStr"/>
-      <c r="G58" s="2" t="inlineStr"/>
-      <c r="H58" s="2" t="inlineStr"/>
-      <c r="I58" s="2" t="inlineStr"/>
+          <t>Owners and tenants[]</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>Are there any agricultural tenants on the land?</t>
+          <t>The title of the individual</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3464,19 +3472,19 @@
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>title</t>
+          <t>first-name</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr"/>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>The title of the individual</t>
+          <t>The first name of the individual</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
@@ -3486,7 +3494,7 @@
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3520,19 +3528,19 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>first-name</t>
+          <t>last-name</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>First Name</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>The first name of the individual</t>
+          <t>The last name of the individual</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
@@ -3576,19 +3584,19 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>last-name</t>
+          <t>address-text</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>Address Text</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr"/>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>The last name of the individual</t>
+          <t>Flexible field for capturing addresses</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
@@ -3632,19 +3640,19 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>address-text</t>
+          <t>postcode</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Postcode</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The postal code</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
@@ -3654,7 +3662,7 @@
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3678,34 +3686,26 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>person</t>
+          <t>notice-date</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="H63" s="2" t="inlineStr">
-        <is>
-          <t>postcode</t>
-        </is>
-      </c>
-      <c r="I63" s="2" t="inlineStr">
-        <is>
-          <t>Postcode</t>
-        </is>
-      </c>
+          <t>Notice date</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr"/>
+      <c r="I63" s="2" t="inlineStr"/>
       <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>Date when notice was served</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -3724,36 +3724,28 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>owners-and-tenants</t>
+          <t>steps-taken</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Owners and tenants[]</t>
-        </is>
-      </c>
-      <c r="F64" s="2" t="inlineStr">
-        <is>
-          <t>notice-date</t>
-        </is>
-      </c>
-      <c r="G64" s="2" t="inlineStr">
-        <is>
-          <t>Notice date</t>
-        </is>
-      </c>
+          <t>Steps taken</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr"/>
+      <c r="G64" s="2" t="inlineStr"/>
       <c r="H64" s="2" t="inlineStr"/>
       <c r="I64" s="2" t="inlineStr"/>
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>Date when notice was served</t>
+          <t>Description of steps taken to identify unknown owners or tenants</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -3772,23 +3764,31 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>steps-taken</t>
+          <t>newspaper-notices</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>Steps taken</t>
-        </is>
-      </c>
-      <c r="F65" s="2" t="inlineStr"/>
-      <c r="G65" s="2" t="inlineStr"/>
+          <t>Newspaper notices[]</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>newspaper-name</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>Newspaper name</t>
+        </is>
+      </c>
       <c r="H65" s="2" t="inlineStr"/>
       <c r="I65" s="2" t="inlineStr"/>
       <c r="J65" s="2" t="inlineStr"/>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>Description of steps taken to identify unknown owners or tenants</t>
+          <t>Name of the newspaper where notice was published</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
@@ -3798,7 +3798,7 @@
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>newspaper-name</t>
+          <t>publication-date</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>Newspaper name</t>
+          <t>Publication date</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr"/>
@@ -3836,12 +3836,12 @@
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>Name of the newspaper where notice was published</t>
+          <t>Date when the notice was published</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -3860,41 +3860,33 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>newspaper-notices</t>
+          <t>ownership-cert-option</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>Newspaper notices[]</t>
-        </is>
-      </c>
-      <c r="F67" s="2" t="inlineStr">
-        <is>
-          <t>publication-date</t>
-        </is>
-      </c>
-      <c r="G67" s="2" t="inlineStr">
-        <is>
-          <t>Publication date</t>
-        </is>
-      </c>
+          <t>Ownership certificate type</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr"/>
+      <c r="G67" s="2" t="inlineStr"/>
       <c r="H67" s="2" t="inlineStr"/>
       <c r="I67" s="2" t="inlineStr"/>
       <c r="J67" s="2" t="inlineStr"/>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>Date when the notice was published</t>
+          <t>The type of ownership certificate based on ownership and tenancy status</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3908,12 +3900,12 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>ownership-cert-option</t>
+          <t>applicant-signature</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Ownership certificate type</t>
+          <t>Applicant signature</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr"/>
@@ -3924,12 +3916,12 @@
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>The type of ownership certificate based on ownership and tenancy status</t>
+          <t>Digital signature of the applicant</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -3948,12 +3940,12 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>applicant-signature</t>
+          <t>agent-signature</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>Applicant signature</t>
+          <t>Agent signature</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr"/>
@@ -3964,7 +3956,7 @@
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>Digital signature of the applicant</t>
+          <t>Digital signature of the agent (if applicable)</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
@@ -3988,12 +3980,12 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>agent-signature</t>
+          <t>declaration-date</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Agent signature</t>
+          <t>Declaration date</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr"/>
@@ -4004,7 +3996,7 @@
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>Digital signature of the agent (if applicable)</t>
+          <t>The date the declaration was made</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
@@ -4019,21 +4011,29 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="2" t="n"/>
-      <c r="B71" s="2" t="n"/>
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>Pre-application advice</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>pre-app-advice</t>
+        </is>
+      </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>Who will be affected by the proposal and whether they have been notified, such as agricultural tenants</t>
+          <t>Details of pre-application advice previously received from the planning authority</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>declaration-date</t>
+          <t>advice-sought</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>Declaration date</t>
+          <t>Pre-application advice sought</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr"/>
@@ -4044,31 +4044,23 @@
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>The date the declaration was made</t>
+          <t>Whether pre-application advice has been sought from the planning authority</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="2" t="inlineStr">
-        <is>
-          <t>Pre-application advice</t>
-        </is>
-      </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>pre-app-advice</t>
-        </is>
-      </c>
+      <c r="A72" s="2" t="n"/>
+      <c r="B72" s="2" t="n"/>
       <c r="C72" s="2" t="inlineStr">
         <is>
           <t>Details of pre-application advice previously received from the planning authority</t>
@@ -4076,12 +4068,12 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>advice-sought</t>
+          <t>officer-name</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Pre-application advice sought</t>
+          <t>Officer name</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr"/>
@@ -4092,17 +4084,17 @@
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>Whether pre-application advice has been sought from the planning authority</t>
+          <t>Name of the planning officer who provided the pre-application advice</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4116,12 +4108,12 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>officer-name</t>
+          <t>reference</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>Officer name</t>
+          <t>Reference</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr"/>
@@ -4132,7 +4124,7 @@
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>Name of the planning officer who provided the pre-application advice</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
@@ -4156,12 +4148,12 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>reference</t>
+          <t>advice-date</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
+          <t>Advice date</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr"/>
@@ -4172,7 +4164,7 @@
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>Date when pre-application advice was received, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
@@ -4196,12 +4188,12 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>advice-date</t>
+          <t>advice-summary</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>Advice date</t>
+          <t>Advice summary</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr"/>
@@ -4212,7 +4204,7 @@
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>Date when pre-application advice was received, in YYYY-MM-DD format</t>
+          <t>Summary of the pre-application advice received from the planning authority</t>
         </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
@@ -4227,37 +4219,53 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="2" t="n"/>
-      <c r="B76" s="2" t="n"/>
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>Site details</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>site-details</t>
+        </is>
+      </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Details of pre-application advice previously received from the planning authority</t>
+          <t>Where the proposed development will be built.</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>advice-summary</t>
+          <t>site-locations</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Advice summary</t>
-        </is>
-      </c>
-      <c r="F76" s="2" t="inlineStr"/>
-      <c r="G76" s="2" t="inlineStr"/>
+          <t>Site locations[]</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>site-boundary</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>Site boundary</t>
+        </is>
+      </c>
       <c r="H76" s="2" t="inlineStr"/>
       <c r="I76" s="2" t="inlineStr"/>
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>Summary of the pre-application advice received from the planning authority</t>
+          <t>Geometry of the site of the development, typically in GeoJSON format</t>
         </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>wkt</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -4267,16 +4275,8 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="inlineStr">
-        <is>
-          <t>Site details</t>
-        </is>
-      </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>site-details</t>
-        </is>
-      </c>
+      <c r="A77" s="2" t="n"/>
+      <c r="B77" s="2" t="n"/>
       <c r="C77" s="2" t="inlineStr">
         <is>
           <t>Where the proposed development will be built.</t>
@@ -4294,12 +4294,12 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>site-boundary</t>
+          <t>address-text</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>Site boundary</t>
+          <t>Address Text</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr"/>
@@ -4308,12 +4308,12 @@
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>Geometry of the site of the development, typically in GeoJSON format</t>
+          <t>Flexible field for capturing addresses</t>
         </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>wkt</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>address-text</t>
+          <t>postcode</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Postcode</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr"/>
@@ -4356,7 +4356,7 @@
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The postal code</t>
         </is>
       </c>
       <c r="M78" s="2" t="inlineStr">
@@ -4390,12 +4390,12 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>postcode</t>
+          <t>easting</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>Postcode</t>
+          <t>Easting</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr"/>
@@ -4404,12 +4404,12 @@
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>Easting coordinate in British National Grid (EPSG:27700)</t>
         </is>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>number</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
@@ -4438,12 +4438,12 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>easting</t>
+          <t>northing</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>Easting</t>
+          <t>Northing</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr"/>
@@ -4452,7 +4452,7 @@
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>Easting coordinate in British National Grid (EPSG:27700)</t>
+          <t>Northing coordinate in British National Grid (EPSG:27700)</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
@@ -4486,12 +4486,12 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>northing</t>
+          <t>latitude</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>Northing</t>
+          <t>Latitude</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr"/>
@@ -4500,7 +4500,7 @@
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>Northing coordinate in British National Grid (EPSG:27700)</t>
+          <t>Latitude coordinate in WGS84 (EPSG:4326)</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
@@ -4534,12 +4534,12 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>latitude</t>
+          <t>longitude</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>Latitude</t>
+          <t>Longitude</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr"/>
@@ -4548,7 +4548,7 @@
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>Latitude coordinate in WGS84 (EPSG:4326)</t>
+          <t>Longitude coordinate in WGS84 (EPSG:4326)</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>longitude</t>
+          <t>description</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>Longitude</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr"/>
@@ -4596,12 +4596,12 @@
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>Longitude coordinate in WGS84 (EPSG:4326)</t>
+          <t>A text description providing details about the subject. For parking changes, this describes how the proposed works affect existing car parking arrangements.</t>
         </is>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
@@ -4630,12 +4630,12 @@
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>uprns</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>UPRNs[]</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr"/>
@@ -4644,7 +4644,7 @@
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>A text description providing details about the subject. For parking changes, this describes how the proposed works affect existing car parking arrangements.</t>
+          <t>Unique Property Reference Numbers (UPRNs) for properties within the site boundary</t>
         </is>
       </c>
       <c r="M84" s="2" t="inlineStr">
@@ -4659,64 +4659,56 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="2" t="n"/>
-      <c r="B85" s="2" t="n"/>
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>Site Visit Details</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>site-visit</t>
+        </is>
+      </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>Where the proposed development will be built.</t>
+          <t>Information to help the planning authority arrange a site visit</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>site-locations</t>
+          <t>can-be-seen-from</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>Site locations[]</t>
-        </is>
-      </c>
-      <c r="F85" s="2" t="inlineStr">
-        <is>
-          <t>uprns</t>
-        </is>
-      </c>
-      <c r="G85" s="2" t="inlineStr">
-        <is>
-          <t>UPRNs[]</t>
-        </is>
-      </c>
+          <t>Site seen from public area</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr"/>
+      <c r="G85" s="2" t="inlineStr"/>
       <c r="H85" s="2" t="inlineStr"/>
       <c r="I85" s="2" t="inlineStr"/>
       <c r="J85" s="2" t="inlineStr"/>
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>Unique Property Reference Numbers (UPRNs) for properties within the site boundary</t>
+          <t>Can site be seen from a public road, public footpath, bridleway or other public land</t>
         </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="2" t="inlineStr">
-        <is>
-          <t>Site Visit Details</t>
-        </is>
-      </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>site-visit</t>
-        </is>
-      </c>
+      <c r="A86" s="2" t="n"/>
+      <c r="B86" s="2" t="n"/>
       <c r="C86" s="2" t="inlineStr">
         <is>
           <t>Information to help the planning authority arrange a site visit</t>
@@ -4724,12 +4716,12 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>can-be-seen-from</t>
+          <t>contact-type</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Site seen from public area</t>
+          <t>Site visit contact type</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr"/>
@@ -4740,12 +4732,12 @@
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>Can site be seen from a public road, public footpath, bridleway or other public land</t>
+          <t>Indicates who the authority should contact to arrange a site visit</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -4764,12 +4756,12 @@
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>contact-type</t>
+          <t>contact-reference</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>Site visit contact type</t>
+          <t>Contact reference</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr"/>
@@ -4780,17 +4772,17 @@
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>Indicates who the authority should contact to arrange a site visit</t>
+          <t>The reference of the applicant or agent who should be contacted for site visits</t>
         </is>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4804,23 +4796,31 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>contact-reference</t>
+          <t>other-contact</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>Contact reference</t>
-        </is>
-      </c>
-      <c r="F88" s="2" t="inlineStr"/>
-      <c r="G88" s="2" t="inlineStr"/>
+          <t>Other site visit contact</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>fullname</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>Full name</t>
+        </is>
+      </c>
       <c r="H88" s="2" t="inlineStr"/>
       <c r="I88" s="2" t="inlineStr"/>
       <c r="J88" s="2" t="inlineStr"/>
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>The reference of the applicant or agent who should be contacted for site visits</t>
+          <t>The complete name of a person</t>
         </is>
       </c>
       <c r="M88" s="2" t="inlineStr">
@@ -4830,7 +4830,7 @@
       </c>
       <c r="N88" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>fullname</t>
+          <t>number</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>Full name</t>
+          <t>Phone number</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr"/>
@@ -4868,7 +4868,7 @@
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>The complete name of a person</t>
+          <t>A phone number</t>
         </is>
       </c>
       <c r="M89" s="2" t="inlineStr">
@@ -4902,12 +4902,12 @@
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>email</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>Phone number</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr"/>
@@ -4916,7 +4916,7 @@
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>The email address that can be used for electronic correspondence with the individual</t>
         </is>
       </c>
       <c r="M90" s="2" t="inlineStr">
@@ -4925,54 +4925,6 @@
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
-        <is>
-          <t>MUST</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="2" t="n"/>
-      <c r="B91" s="2" t="n"/>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t>Information to help the planning authority arrange a site visit</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
-        <is>
-          <t>other-contact</t>
-        </is>
-      </c>
-      <c r="E91" s="2" t="inlineStr">
-        <is>
-          <t>Other site visit contact</t>
-        </is>
-      </c>
-      <c r="F91" s="2" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="G91" s="2" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="H91" s="2" t="inlineStr"/>
-      <c r="I91" s="2" t="inlineStr"/>
-      <c r="J91" s="2" t="inlineStr"/>
-      <c r="K91" s="2" t="inlineStr"/>
-      <c r="L91" s="2" t="inlineStr">
-        <is>
-          <t>The email address that can be used for electronic correspondence with the individual</t>
-        </is>
-      </c>
-      <c r="M91" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="N91" s="2" t="inlineStr">
         <is>
           <t>MUST</t>
         </is>
@@ -4980,34 +4932,34 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="A43"/>
-    <mergeCell ref="A2:A19"/>
-    <mergeCell ref="A24:A31"/>
-    <mergeCell ref="A49:A56"/>
-    <mergeCell ref="A36:A41"/>
-    <mergeCell ref="A72:A76"/>
-    <mergeCell ref="B57:B71"/>
-    <mergeCell ref="B86:B91"/>
-    <mergeCell ref="B72:B76"/>
-    <mergeCell ref="B44:B45"/>
-    <mergeCell ref="A32:A35"/>
-    <mergeCell ref="B43"/>
-    <mergeCell ref="A57:A71"/>
-    <mergeCell ref="A86:A91"/>
-    <mergeCell ref="A20:A23"/>
-    <mergeCell ref="A77:A85"/>
-    <mergeCell ref="B46:B48"/>
+    <mergeCell ref="B35:B40"/>
+    <mergeCell ref="B31:B34"/>
+    <mergeCell ref="B43:B44"/>
+    <mergeCell ref="B56:B70"/>
+    <mergeCell ref="A48:A55"/>
+    <mergeCell ref="A71:A75"/>
+    <mergeCell ref="B41"/>
+    <mergeCell ref="B2:B18"/>
+    <mergeCell ref="A76:A84"/>
+    <mergeCell ref="B45:B47"/>
+    <mergeCell ref="B19:B22"/>
+    <mergeCell ref="A56:A70"/>
+    <mergeCell ref="B23:B30"/>
+    <mergeCell ref="A45:A47"/>
+    <mergeCell ref="B48:B55"/>
+    <mergeCell ref="B71:B75"/>
+    <mergeCell ref="A2:A18"/>
+    <mergeCell ref="B76:B84"/>
+    <mergeCell ref="A85:A90"/>
     <mergeCell ref="B42"/>
-    <mergeCell ref="A44:A45"/>
-    <mergeCell ref="B36:B41"/>
-    <mergeCell ref="B49:B56"/>
-    <mergeCell ref="B20:B23"/>
-    <mergeCell ref="B2:B19"/>
-    <mergeCell ref="B24:B31"/>
+    <mergeCell ref="A41"/>
+    <mergeCell ref="A19:A22"/>
+    <mergeCell ref="A43:A44"/>
+    <mergeCell ref="A35:A40"/>
+    <mergeCell ref="A31:A34"/>
+    <mergeCell ref="A23:A30"/>
     <mergeCell ref="A42"/>
-    <mergeCell ref="A46:A48"/>
-    <mergeCell ref="B77:B85"/>
-    <mergeCell ref="B32:B35"/>
+    <mergeCell ref="B85:B90"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/generated/spreadsheet/verbose/removal-or-variation-of-a-condition-following-grant-of-planning-permission-s73-verbose.xlsx
+++ b/generated/spreadsheet/verbose/removal-or-variation-of-a-condition-following-grant-of-planning-permission-s73-verbose.xlsx
@@ -3089,7 +3089,7 @@
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">

--- a/generated/spreadsheet/verbose/removal-or-variation-of-a-condition-following-grant-of-planning-permission-s73-verbose.xlsx
+++ b/generated/spreadsheet/verbose/removal-or-variation-of-a-condition-following-grant-of-planning-permission-s73-verbose.xlsx
@@ -2937,7 +2937,7 @@
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -4001,7 +4001,7 @@
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -4169,7 +4169,7 @@
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">

--- a/generated/spreadsheet/verbose/removal-or-variation-of-a-condition-following-grant-of-planning-permission-s73-verbose.xlsx
+++ b/generated/spreadsheet/verbose/removal-or-variation-of-a-condition-following-grant-of-planning-permission-s73-verbose.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N90"/>
+  <dimension ref="A1:N91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
@@ -435,14 +435,14 @@
     <col width="72" customWidth="1" min="3" max="3"/>
     <col width="28" customWidth="1" min="4" max="4"/>
     <col width="31" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="21" customWidth="1" min="7" max="7"/>
+    <col width="23" customWidth="1" min="6" max="6"/>
+    <col width="23" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
     <col width="18" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="11" customWidth="1" min="11" max="11"/>
     <col width="72" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
     <col width="13" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
@@ -521,37 +521,37 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>reference</t>
+          <t>submission-reference</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
+          <t>Submission reference</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr"/>
@@ -560,7 +560,7 @@
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>A unique reference for the submission</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
@@ -579,17 +579,17 @@
       <c r="B3" s="2" t="n"/>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -627,27 +627,27 @@
       <c r="B4" s="2" t="n"/>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>planning-authority</t>
+          <t>specification-profile</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Planning authority</t>
+          <t>Specification profile</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr"/>
@@ -656,7 +656,7 @@
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>A reference of the planning authority the application has been submitted to, e.g. local-authority:CMD for London borough of Camden</t>
+          <t>The specification profile used to determine context-specific allowed codelist values for the application</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -675,27 +675,27 @@
       <c r="B5" s="2" t="n"/>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>submission-date</t>
+          <t>planning-authority</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Submission date</t>
+          <t>Planning authority</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr"/>
@@ -704,12 +704,12 @@
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>Date the application is submitted in YYYY-MM-DD format</t>
+          <t>A reference of the planning authority the application has been submitted to, e.g. local-authority:CMD for London borough of Camden</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -723,27 +723,27 @@
       <c r="B6" s="2" t="n"/>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>modules</t>
+          <t>submitted-at</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Modules[]</t>
+          <t>Submitted at</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr"/>
@@ -752,12 +752,12 @@
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>List of required modules for this application that can be used to validate the application</t>
+          <t>The date and time the application was submitted</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -771,49 +771,41 @@
       <c r="B7" s="2" t="n"/>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>documents</t>
+          <t>created-at</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Documents[]</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>reference</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>Reference</t>
-        </is>
-      </c>
+          <t>Created at</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr"/>
+      <c r="I7" s="2" t="inlineStr"/>
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>Unique reference for the document within this application submission, generated by the submitting system</t>
+          <t>The date and time the submission payload was created</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -827,17 +819,17 @@
       <c r="B8" s="2" t="n"/>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -852,19 +844,19 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>reference</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Reference</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>The name or title of the document</t>
+          <t>Unique reference for the document within this application submission, generated by the submitting system</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -883,17 +875,17 @@
       <c r="B9" s="2" t="n"/>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -908,19 +900,19 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>name</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>Brief description of what the document contains</t>
+          <t>The name or title of the document</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -930,7 +922,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -939,17 +931,17 @@
       <c r="B10" s="2" t="n"/>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -964,29 +956,29 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>document-types</t>
+          <t>description</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>Document types[]</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>List of codelist references that the document covers</t>
+          <t>Brief description of what the document contains</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -995,17 +987,17 @@
       <c r="B11" s="2" t="n"/>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1020,24 +1012,24 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>uploaded-date</t>
+          <t>document-types</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>Uploaded date</t>
+          <t>Document types[]</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>The date the document was uploaded to the application</t>
+          <t>List of codelist references that the document covers</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1051,17 +1043,17 @@
       <c r="B12" s="2" t="n"/>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1076,37 +1068,29 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>file</t>
+          <t>uploaded-date</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>File</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>base64-content</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>Base64</t>
-        </is>
-      </c>
+          <t>Uploaded date</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>Base64-encoded content of the file for inline file uploads</t>
+          <t>The date the document was uploaded to the application</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1115,17 +1099,17 @@
       <c r="B13" s="2" t="n"/>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1150,17 +1134,17 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>filename</t>
+          <t>base64-content</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>Filename</t>
+          <t>Base64</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>Name of the file being uploaded</t>
+          <t>Base64-encoded content of the file for inline file uploads</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -1170,7 +1154,7 @@
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1179,17 +1163,17 @@
       <c r="B14" s="2" t="n"/>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1214,17 +1198,17 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>mime-type</t>
+          <t>filename</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>MIME type</t>
+          <t>Filename</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>The file's MIME type such as application/pdf or image/jpeg</t>
+          <t>Name of the file being uploaded</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1234,7 +1218,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1243,17 +1227,17 @@
       <c r="B15" s="2" t="n"/>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1278,22 +1262,22 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>file-size</t>
+          <t>mime-type</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>File size</t>
+          <t>MIME type</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>Size of the file in bytes that can be used to enforce limits</t>
+          <t>The file's MIME type such as application/pdf or image/jpeg</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1307,54 +1291,62 @@
       <c r="B16" s="2" t="n"/>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>fee</t>
+          <t>documents</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Fee</t>
+          <t>Documents[]</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>amount</t>
+          <t>file</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>Amount</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr"/>
-      <c r="K16" s="2" t="inlineStr"/>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>file-size</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>File size</t>
+        </is>
+      </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>The total amount due for the application fee</t>
+          <t>Size of the file in bytes that can be used to enforce limits</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1363,17 +1355,17 @@
       <c r="B17" s="2" t="n"/>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1388,24 +1380,24 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>amount-paid</t>
+          <t>amount</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>Amount paid</t>
+          <t>Amount</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr"/>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>The amount paid towards the application fee</t>
+          <t>The total amount due for the application fee</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1419,17 +1411,17 @@
       <c r="B18" s="2" t="n"/>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1444,67 +1436,75 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>transactions</t>
+          <t>amount-paid</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>Transactions[]</t>
+          <t>Amount paid</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>References to payments or financial transactions related to this application</t>
+          <t>The amount paid towards the application fee</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>Agent contact details</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>agent-contact</t>
-        </is>
-      </c>
+      <c r="A19" s="2" t="n"/>
+      <c r="B19" s="2" t="n"/>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Name and contact information if an agent is being used.</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>agent-reference</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Agent reference</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr"/>
-      <c r="G19" s="2" t="inlineStr"/>
-      <c r="H19" s="2" t="inlineStr"/>
-      <c r="I19" s="2" t="inlineStr"/>
+          <t>Submission details</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>fee</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>Fee</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>transactions</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>Transactions[]</t>
+        </is>
+      </c>
       <c r="J19" s="2" t="inlineStr"/>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>A reference to an agent object</t>
+          <t>References to payments or financial transactions related to this application</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
@@ -1514,13 +1514,21 @@
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="n"/>
-      <c r="B20" s="2" t="n"/>
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Agent contact details</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>agent-contact</t>
+        </is>
+      </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
           <t>Name and contact information if an agent is being used.</t>
@@ -1528,31 +1536,23 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>contact-details</t>
+          <t>agent-reference</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Contact details</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
+          <t>Agent reference</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr"/>
+      <c r="G20" s="2" t="inlineStr"/>
       <c r="H20" s="2" t="inlineStr"/>
       <c r="I20" s="2" t="inlineStr"/>
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>The email address that can be used for electronic correspondence with the individual</t>
+          <t>A reference to an agent object</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1586,29 +1586,21 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>phone-numbers</t>
+          <t>email</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>Phone number(s)[]</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>number</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>Phone number</t>
-        </is>
-      </c>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr"/>
+      <c r="I21" s="2" t="inlineStr"/>
       <c r="J21" s="2" t="inlineStr"/>
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>The email address that can be used for electronic correspondence with the individual</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
@@ -1618,7 +1610,7 @@
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1652,24 +1644,24 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>contact-priority</t>
+          <t>number</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>Contact priority</t>
+          <t>Phone number</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr"/>
       <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>The priority of a number</t>
+          <t>A phone number</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -1679,16 +1671,8 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>Agent details</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>agent-details</t>
-        </is>
-      </c>
+      <c r="A23" s="2" t="n"/>
+      <c r="B23" s="2" t="n"/>
       <c r="C23" s="2" t="inlineStr">
         <is>
           <t>Name and contact information if an agent is being used.</t>
@@ -1696,47 +1680,63 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>agent</t>
+          <t>contact-details</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>agent</t>
+          <t>Contact details</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>reference</t>
+          <t>phone-numbers</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr"/>
-      <c r="I23" s="2" t="inlineStr"/>
+          <t>Phone number(s)[]</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>contact-priority</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>Contact priority</t>
+        </is>
+      </c>
       <c r="J23" s="2" t="inlineStr"/>
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>The priority of a number</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="n"/>
-      <c r="B24" s="2" t="n"/>
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Agent details</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>agent-details</t>
+        </is>
+      </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
           <t>Name and contact information if an agent is being used.</t>
@@ -1754,29 +1754,21 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>person</t>
+          <t>reference</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr"/>
+      <c r="I24" s="2" t="inlineStr"/>
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>The title of the individual</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
@@ -1786,7 +1778,7 @@
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1820,19 +1812,19 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>first-name</t>
+          <t>title</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>First Name</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr"/>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>The first name of the individual</t>
+          <t>The title of the individual</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
@@ -1842,7 +1834,7 @@
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1876,19 +1868,19 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>last-name</t>
+          <t>first-name</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr"/>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>The last name of the individual</t>
+          <t>The first name of the individual</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -1932,19 +1924,19 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>address-text</t>
+          <t>last-name</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr"/>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The last name of the individual</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
@@ -1988,19 +1980,19 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>postcode</t>
+          <t>address-text</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>Postcode</t>
+          <t>Address Text</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>Flexible field for capturing addresses</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
@@ -2010,7 +2002,7 @@
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2034,21 +2026,29 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>company</t>
+          <t>person</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Company</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr"/>
-      <c r="I29" s="2" t="inlineStr"/>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>postcode</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>Postcode</t>
+        </is>
+      </c>
       <c r="J29" s="2" t="inlineStr"/>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>The name of a company (that the agent works for)</t>
+          <t>The postal code</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
@@ -2082,12 +2082,12 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>user-role</t>
+          <t>company</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>User role</t>
+          <t>Company</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr"/>
@@ -2096,12 +2096,12 @@
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>The role of the named individual. Agent or proxy</t>
+          <t>The name of a company (that the agent works for)</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -2111,56 +2111,64 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>Applicant contact details</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>applicant-contact</t>
-        </is>
-      </c>
+      <c r="A31" s="2" t="n"/>
+      <c r="B31" s="2" t="n"/>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Telephone number and email address of the applicant.</t>
+          <t>Name and contact information if an agent is being used.</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>applicant-reference</t>
+          <t>agent</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Applicant reference</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr"/>
-      <c r="G31" s="2" t="inlineStr"/>
+          <t>agent</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>user-role</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>User role</t>
+        </is>
+      </c>
       <c r="H31" s="2" t="inlineStr"/>
       <c r="I31" s="2" t="inlineStr"/>
       <c r="J31" s="2" t="inlineStr"/>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>Reference to match contact details to a named individual from the applicant details component</t>
+          <t>The role of the named individual. Agent or proxy</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="n"/>
-      <c r="B32" s="2" t="n"/>
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>Applicant contact details</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>applicant-contact</t>
+        </is>
+      </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
           <t>Telephone number and email address of the applicant.</t>
@@ -2168,31 +2176,23 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>contact-details</t>
+          <t>applicant-reference</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Contact details</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
+          <t>Applicant reference</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr"/>
+      <c r="G32" s="2" t="inlineStr"/>
       <c r="H32" s="2" t="inlineStr"/>
       <c r="I32" s="2" t="inlineStr"/>
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>The email address that can be used for electronic correspondence with the individual</t>
+          <t>Reference to match contact details to a named individual from the applicant details component</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
@@ -2226,29 +2226,21 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>phone-numbers</t>
+          <t>email</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>Phone number(s)[]</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>number</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>Phone number</t>
-        </is>
-      </c>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr"/>
+      <c r="I33" s="2" t="inlineStr"/>
       <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>The email address that can be used for electronic correspondence with the individual</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
@@ -2258,7 +2250,7 @@
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2292,24 +2284,24 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>contact-priority</t>
+          <t>number</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>Contact priority</t>
+          <t>Phone number</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>The priority of a number</t>
+          <t>A phone number</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -2319,64 +2311,72 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>Applicant details</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>applicant-details</t>
-        </is>
-      </c>
+      <c r="A35" s="2" t="n"/>
+      <c r="B35" s="2" t="n"/>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Name and contact information for the parties making the application.</t>
+          <t>Telephone number and email address of the applicant.</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>applicants</t>
+          <t>contact-details</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Applicants[]</t>
+          <t>Contact details</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>reference</t>
+          <t>phone-numbers</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr"/>
-      <c r="I35" s="2" t="inlineStr"/>
+          <t>Phone number(s)[]</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>contact-priority</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>Contact priority</t>
+        </is>
+      </c>
       <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>The priority of a number</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="n"/>
-      <c r="B36" s="2" t="n"/>
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>Applicant details</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>applicant-details</t>
+        </is>
+      </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
           <t>Name and contact information for the parties making the application.</t>
@@ -2394,29 +2394,21 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>person</t>
+          <t>reference</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr"/>
+      <c r="I36" s="2" t="inlineStr"/>
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>The title of the individual</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
@@ -2426,7 +2418,7 @@
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2460,19 +2452,19 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>first-name</t>
+          <t>title</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>First Name</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr"/>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>The first name of the individual</t>
+          <t>The title of the individual</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
@@ -2482,7 +2474,7 @@
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2516,19 +2508,19 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>last-name</t>
+          <t>first-name</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>The last name of the individual</t>
+          <t>The first name of the individual</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
@@ -2572,19 +2564,19 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>address-text</t>
+          <t>last-name</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The last name of the individual</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
@@ -2628,19 +2620,19 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>postcode</t>
+          <t>address-text</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>Postcode</t>
+          <t>Address Text</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>Flexible field for capturing addresses</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
@@ -2650,45 +2642,53 @@
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>Checklist</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>checklist</t>
-        </is>
-      </c>
+      <c r="A41" s="2" t="n"/>
+      <c r="B41" s="2" t="n"/>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Checking whether all the requirements of the form have been met, such as proof of payment or supporting documentation.</t>
+          <t>Name and contact information for the parties making the application.</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>national-req-types</t>
+          <t>applicants</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>National requirement types[]</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr"/>
-      <c r="G41" s="2" t="inlineStr"/>
-      <c r="H41" s="2" t="inlineStr"/>
-      <c r="I41" s="2" t="inlineStr"/>
+          <t>Applicants[]</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>postcode</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>Postcode</t>
+        </is>
+      </c>
       <c r="J41" s="2" t="inlineStr"/>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>List of the document types required for the given application type</t>
+          <t>The postal code</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
@@ -2698,89 +2698,97 @@
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Conflict of interest</t>
+          <t>Checklist</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>conflict-of-interest</t>
+          <t>checklist</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Details of any conflict of interest that may exist between the applicant and planning authority.</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr"/>
-      <c r="E42" s="2" t="inlineStr"/>
+          <t>Checking whether all the requirements of the form have been met, such as proof of payment or supporting documentation.</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>national-req-types</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>National requirement types[]</t>
+        </is>
+      </c>
       <c r="F42" s="2" t="inlineStr"/>
       <c r="G42" s="2" t="inlineStr"/>
       <c r="H42" s="2" t="inlineStr"/>
       <c r="I42" s="2" t="inlineStr"/>
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr"/>
-      <c r="L42" s="2" t="inlineStr"/>
-      <c r="M42" s="2" t="inlineStr"/>
-      <c r="N42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>List of the document types required for the given application type</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>Condition removal or variation</t>
+          <t>Conflict of interest</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>con-remove-vary</t>
+          <t>conflict-of-interest</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Why the applicant is asking for planning conditions to be removed or changed.</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>reason</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>Reason</t>
-        </is>
-      </c>
+          <t>Details of any conflict of interest that may exist between the applicant and planning authority.</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr"/>
+      <c r="E43" s="2" t="inlineStr"/>
       <c r="F43" s="2" t="inlineStr"/>
       <c r="G43" s="2" t="inlineStr"/>
       <c r="H43" s="2" t="inlineStr"/>
       <c r="I43" s="2" t="inlineStr"/>
       <c r="J43" s="2" t="inlineStr"/>
       <c r="K43" s="2" t="inlineStr"/>
-      <c r="L43" s="2" t="inlineStr">
-        <is>
-          <t>The reason why the applicant wishes condition(s) to be removed or changed</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="N43" s="2" t="inlineStr">
-        <is>
-          <t>MUST</t>
-        </is>
-      </c>
+      <c r="L43" s="2" t="inlineStr"/>
+      <c r="M43" s="2" t="inlineStr"/>
+      <c r="N43" s="2" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="n"/>
-      <c r="B44" s="2" t="n"/>
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>Condition removal or variation</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>con-remove-vary</t>
+        </is>
+      </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
           <t>Why the applicant is asking for planning conditions to be removed or changed.</t>
@@ -2788,12 +2796,12 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>condition-change</t>
+          <t>reason</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Condition change</t>
+          <t>Reason</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr"/>
@@ -2804,7 +2812,7 @@
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>State how the condition should vary</t>
+          <t>The reason why the applicant wishes condition(s) to be removed or changed</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
@@ -2814,34 +2822,26 @@
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>Declaration</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>declaration</t>
-        </is>
-      </c>
+      <c r="A45" s="2" t="n"/>
+      <c r="B45" s="2" t="n"/>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Signed and dated verification of the application's accuracy.</t>
+          <t>Why the applicant is asking for planning conditions to be removed or changed.</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>condition-change</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Condition change</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr"/>
@@ -2852,7 +2852,7 @@
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>A name of a person</t>
+          <t>State how the condition should vary</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
@@ -2862,13 +2862,21 @@
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="n"/>
-      <c r="B46" s="2" t="n"/>
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>Declaration</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>declaration</t>
+        </is>
+      </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
           <t>Signed and dated verification of the application's accuracy.</t>
@@ -2876,12 +2884,12 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>declaration-confirmed</t>
+          <t>person-reference</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Declaration confirmed</t>
+          <t>Person reference</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr"/>
@@ -2892,12 +2900,12 @@
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
+          <t>Declaration must be made by an applicant or agent making the application</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -2916,12 +2924,12 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>declaration-date</t>
+          <t>declaration-confirmed</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>Declaration date</t>
+          <t>Declaration confirmed</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr"/>
@@ -2932,12 +2940,12 @@
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>The date the declaration was made</t>
+          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -2947,53 +2955,37 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>Description of your proposal</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>desc-your-proposal</t>
-        </is>
-      </c>
+      <c r="A48" s="2" t="n"/>
+      <c r="B48" s="2" t="n"/>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Written description of the proposed development including any additional relevant details.</t>
+          <t>Signed and dated verification of the application's accuracy.</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>related-application</t>
+          <t>declaration-date</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Related application</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>reference</t>
-        </is>
-      </c>
-      <c r="G48" s="2" t="inlineStr">
-        <is>
-          <t>Reference</t>
-        </is>
-      </c>
+          <t>Declaration date</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr"/>
+      <c r="G48" s="2" t="inlineStr"/>
       <c r="H48" s="2" t="inlineStr"/>
       <c r="I48" s="2" t="inlineStr"/>
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>The reference for the related application</t>
+          <t>The date the declaration was made</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -3003,8 +2995,16 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="n"/>
-      <c r="B49" s="2" t="n"/>
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>Description of your proposal</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>desc-your-proposal</t>
+        </is>
+      </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
           <t>Written description of the proposed development including any additional relevant details.</t>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>reference</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Reference</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr"/>
@@ -3036,7 +3036,7 @@
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>A description of the related application</t>
+          <t>The reference for the related application</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
@@ -3070,12 +3070,12 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>decision-date</t>
+          <t>description</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>Decision date</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr"/>
@@ -3084,17 +3084,17 @@
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>The date when the decision was made, in YYYY-MM-DD format</t>
+          <t>A description of the related application</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3108,28 +3108,36 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>condition-numbers</t>
+          <t>related-application</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>Condition numbers[]</t>
-        </is>
-      </c>
-      <c r="F51" s="2" t="inlineStr"/>
-      <c r="G51" s="2" t="inlineStr"/>
+          <t>Related application</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>decision-date</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>Decision date</t>
+        </is>
+      </c>
       <c r="H51" s="2" t="inlineStr"/>
       <c r="I51" s="2" t="inlineStr"/>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>List of condition numbers related to this application</t>
+          <t>The date when the decision was made, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -3148,12 +3156,12 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>has-development-started</t>
+          <t>condition-numbers</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Has development started</t>
+          <t>Condition numbers[]</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr"/>
@@ -3164,17 +3172,17 @@
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>Whether the development has already started</t>
+          <t>List of condition numbers related to this application</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3188,12 +3196,12 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>development-start-date</t>
+          <t>has-development-started</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>Development start date</t>
+          <t>Has development started</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr"/>
@@ -3204,17 +3212,17 @@
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>Date when development started</t>
+          <t>Whether the development has already started</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3236,12 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>has-development-completed</t>
+          <t>development-start-date</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Has development completed</t>
+          <t>Development start date</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr"/>
@@ -3244,17 +3252,17 @@
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>Whether the development has been completed</t>
+          <t>Date when development started</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3268,12 +3276,12 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>development-completed-date</t>
+          <t>has-development-completed</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>Development completed date</t>
+          <t>Has development completed</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr"/>
@@ -3284,44 +3292,36 @@
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>Date when development was completed</t>
+          <t>Whether the development has been completed</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>Ownership certificates and agricultural land declaration</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>ownership-certs</t>
-        </is>
-      </c>
+      <c r="A56" s="2" t="n"/>
+      <c r="B56" s="2" t="n"/>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Who will be affected by the proposal and whether they have been notified, such as agricultural tenants</t>
+          <t>Written description of the proposed development including any additional relevant details.</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>sole-owner</t>
+          <t>development-completed-date</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Sole owner</t>
+          <t>Development completed date</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr"/>
@@ -3332,23 +3332,31 @@
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>Is the applicant the sole owner of the land?</t>
+          <t>Date when development was completed</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="n"/>
-      <c r="B57" s="2" t="n"/>
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>Ownership certificates and agricultural land declaration</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>ownership-certs</t>
+        </is>
+      </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
           <t>Who will be affected by the proposal and whether they have been notified, such as agricultural tenants</t>
@@ -3356,12 +3364,12 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>agricultural-tenants</t>
+          <t>sole-owner</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>Agricultural tenants</t>
+          <t>Sole owner</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr"/>
@@ -3372,7 +3380,7 @@
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>Are there any agricultural tenants on the land?</t>
+          <t>Is the applicant the sole owner of the land?</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
@@ -3396,49 +3404,33 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>owners-and-tenants</t>
+          <t>agricultural-tenants</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Owners and tenants[]</t>
-        </is>
-      </c>
-      <c r="F58" s="2" t="inlineStr">
-        <is>
-          <t>person</t>
-        </is>
-      </c>
-      <c r="G58" s="2" t="inlineStr">
-        <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="H58" s="2" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="I58" s="2" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
+          <t>Agricultural tenants</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr"/>
+      <c r="G58" s="2" t="inlineStr"/>
+      <c r="H58" s="2" t="inlineStr"/>
+      <c r="I58" s="2" t="inlineStr"/>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>The title of the individual</t>
+          <t>Are there any agricultural tenants on the land?</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3472,19 +3464,19 @@
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>first-name</t>
+          <t>title</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>First Name</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr"/>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>The first name of the individual</t>
+          <t>The title of the individual</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
@@ -3494,7 +3486,7 @@
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3528,19 +3520,19 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>last-name</t>
+          <t>first-name</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>The last name of the individual</t>
+          <t>The first name of the individual</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
@@ -3584,19 +3576,19 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>address-text</t>
+          <t>last-name</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr"/>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The last name of the individual</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
@@ -3640,19 +3632,19 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>postcode</t>
+          <t>address-text</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>Postcode</t>
+          <t>Address Text</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>Flexible field for capturing addresses</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
@@ -3662,7 +3654,7 @@
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3686,26 +3678,34 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>notice-date</t>
+          <t>person</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>Notice date</t>
-        </is>
-      </c>
-      <c r="H63" s="2" t="inlineStr"/>
-      <c r="I63" s="2" t="inlineStr"/>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>postcode</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>Postcode</t>
+        </is>
+      </c>
       <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>Date when notice was served</t>
+          <t>The postal code</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -3724,28 +3724,36 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>steps-taken</t>
+          <t>owners-and-tenants</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Steps taken</t>
-        </is>
-      </c>
-      <c r="F64" s="2" t="inlineStr"/>
-      <c r="G64" s="2" t="inlineStr"/>
+          <t>Owners and tenants[]</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>notice-served-date</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>Notice served date</t>
+        </is>
+      </c>
       <c r="H64" s="2" t="inlineStr"/>
       <c r="I64" s="2" t="inlineStr"/>
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>Description of steps taken to identify unknown owners or tenants</t>
+          <t>Date when notice was served</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -3764,41 +3772,33 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>newspaper-notices</t>
+          <t>ownership-cert-option</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>Newspaper notices[]</t>
-        </is>
-      </c>
-      <c r="F65" s="2" t="inlineStr">
-        <is>
-          <t>newspaper-name</t>
-        </is>
-      </c>
-      <c r="G65" s="2" t="inlineStr">
-        <is>
-          <t>Newspaper name</t>
-        </is>
-      </c>
+          <t>Ownership certificate type</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr"/>
+      <c r="G65" s="2" t="inlineStr"/>
       <c r="H65" s="2" t="inlineStr"/>
       <c r="I65" s="2" t="inlineStr"/>
       <c r="J65" s="2" t="inlineStr"/>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>Name of the newspaper where notice was published</t>
+          <t>The type of ownership certificate based on ownership and tenancy status</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3812,41 +3812,33 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>newspaper-notices</t>
+          <t>steps-taken</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Newspaper notices[]</t>
-        </is>
-      </c>
-      <c r="F66" s="2" t="inlineStr">
-        <is>
-          <t>publication-date</t>
-        </is>
-      </c>
-      <c r="G66" s="2" t="inlineStr">
-        <is>
-          <t>Publication date</t>
-        </is>
-      </c>
+          <t>Steps taken</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr"/>
+      <c r="G66" s="2" t="inlineStr"/>
       <c r="H66" s="2" t="inlineStr"/>
       <c r="I66" s="2" t="inlineStr"/>
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>Date when the notice was published</t>
+          <t>Description of steps taken to identify unknown owners or tenants</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3860,33 +3852,41 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>ownership-cert-option</t>
+          <t>newspaper-notices</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>Ownership certificate type</t>
-        </is>
-      </c>
-      <c r="F67" s="2" t="inlineStr"/>
-      <c r="G67" s="2" t="inlineStr"/>
+          <t>Newspaper notices[]</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>newspaper-name</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>Newspaper name</t>
+        </is>
+      </c>
       <c r="H67" s="2" t="inlineStr"/>
       <c r="I67" s="2" t="inlineStr"/>
       <c r="J67" s="2" t="inlineStr"/>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>The type of ownership certificate based on ownership and tenancy status</t>
+          <t>Name of the newspaper where notice was published</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3900,33 +3900,41 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>applicant-signature</t>
+          <t>newspaper-notices</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Applicant signature</t>
-        </is>
-      </c>
-      <c r="F68" s="2" t="inlineStr"/>
-      <c r="G68" s="2" t="inlineStr"/>
+          <t>Newspaper notices[]</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>publication-date</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>Publication date</t>
+        </is>
+      </c>
       <c r="H68" s="2" t="inlineStr"/>
       <c r="I68" s="2" t="inlineStr"/>
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>Digital signature of the applicant</t>
+          <t>Date when the notice was published</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3940,12 +3948,12 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>agent-signature</t>
+          <t>person-reference</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>Agent signature</t>
+          <t>Person reference</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr"/>
@@ -3956,7 +3964,7 @@
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>Digital signature of the agent (if applicable)</t>
+          <t>Declaration must be made by an applicant or agent making the application</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
@@ -3966,7 +3974,7 @@
       </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3980,12 +3988,12 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>declaration-date</t>
+          <t>declaration-confirmed</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Declaration date</t>
+          <t>Declaration confirmed</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr"/>
@@ -3996,44 +4004,36 @@
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>The date the declaration was made</t>
+          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="2" t="inlineStr">
-        <is>
-          <t>Pre-application advice</t>
-        </is>
-      </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>pre-app-advice</t>
-        </is>
-      </c>
+      <c r="A71" s="2" t="n"/>
+      <c r="B71" s="2" t="n"/>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>Details of pre-application advice previously received from the planning authority</t>
+          <t>Who will be affected by the proposal and whether they have been notified, such as agricultural tenants</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>advice-sought</t>
+          <t>declaration-date</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>Pre-application advice sought</t>
+          <t>Declaration date</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr"/>
@@ -4044,12 +4044,12 @@
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>Whether pre-application advice has been sought from the planning authority</t>
+          <t>The date the declaration was made</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
@@ -4059,8 +4059,16 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="2" t="n"/>
-      <c r="B72" s="2" t="n"/>
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>Pre-application advice</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>pre-app-advice</t>
+        </is>
+      </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
           <t>Details of pre-application advice previously received from the planning authority</t>
@@ -4068,12 +4076,12 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>officer-name</t>
+          <t>advice-sought</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Officer name</t>
+          <t>Pre-application advice sought</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr"/>
@@ -4084,17 +4092,17 @@
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>Name of the planning officer who provided the pre-application advice</t>
+          <t>Whether pre-application advice has been sought from the planning authority</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4108,12 +4116,12 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>reference</t>
+          <t>officer-name</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
+          <t>Officer name</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr"/>
@@ -4124,7 +4132,7 @@
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>Name of the planning officer who provided the pre-application advice</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
@@ -4148,12 +4156,12 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>advice-date</t>
+          <t>reference</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Advice date</t>
+          <t>Reference</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr"/>
@@ -4164,12 +4172,12 @@
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>Date when pre-application advice was received, in YYYY-MM-DD format</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -4188,12 +4196,12 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>advice-summary</t>
+          <t>advice-date</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>Advice summary</t>
+          <t>Advice date</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr"/>
@@ -4204,12 +4212,12 @@
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>Summary of the pre-application advice received from the planning authority</t>
+          <t>Date when pre-application advice was received, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
@@ -4219,53 +4227,37 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="2" t="inlineStr">
-        <is>
-          <t>Site details</t>
-        </is>
-      </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>site-details</t>
-        </is>
-      </c>
+      <c r="A76" s="2" t="n"/>
+      <c r="B76" s="2" t="n"/>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Where the proposed development will be built.</t>
+          <t>Details of pre-application advice previously received from the planning authority</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>site-locations</t>
+          <t>advice-summary</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Site locations[]</t>
-        </is>
-      </c>
-      <c r="F76" s="2" t="inlineStr">
-        <is>
-          <t>site-boundary</t>
-        </is>
-      </c>
-      <c r="G76" s="2" t="inlineStr">
-        <is>
-          <t>Site boundary</t>
-        </is>
-      </c>
+          <t>Advice summary</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr"/>
+      <c r="G76" s="2" t="inlineStr"/>
       <c r="H76" s="2" t="inlineStr"/>
       <c r="I76" s="2" t="inlineStr"/>
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>Geometry of the site of the development, typically in GeoJSON format</t>
+          <t>Summary of the pre-application advice received from the planning authority</t>
         </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>wkt</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -4275,8 +4267,16 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="n"/>
-      <c r="B77" s="2" t="n"/>
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>Site details</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>site-details</t>
+        </is>
+      </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
           <t>Where the proposed development will be built.</t>
@@ -4294,12 +4294,12 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>address-text</t>
+          <t>site-boundary</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Site boundary</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr"/>
@@ -4308,12 +4308,12 @@
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>Geometry of the site of the development, typically in GeoJSON format</t>
         </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>wkt</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>postcode</t>
+          <t>address-text</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>Postcode</t>
+          <t>Address Text</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr"/>
@@ -4356,7 +4356,7 @@
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>Flexible field for capturing addresses</t>
         </is>
       </c>
       <c r="M78" s="2" t="inlineStr">
@@ -4390,12 +4390,12 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>easting</t>
+          <t>postcode</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>Easting</t>
+          <t>Postcode</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr"/>
@@ -4404,12 +4404,12 @@
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>Easting coordinate in British National Grid (EPSG:27700)</t>
+          <t>The postal code</t>
         </is>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
@@ -4438,12 +4438,12 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>northing</t>
+          <t>easting</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>Northing</t>
+          <t>Easting</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr"/>
@@ -4452,12 +4452,12 @@
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>Northing coordinate in British National Grid (EPSG:27700)</t>
+          <t>Easting coordinate in British National Grid (EPSG:27700)</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -4486,12 +4486,12 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>latitude</t>
+          <t>northing</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>Latitude</t>
+          <t>Northing</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr"/>
@@ -4500,12 +4500,12 @@
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>Latitude coordinate in WGS84 (EPSG:4326)</t>
+          <t>Northing coordinate in British National Grid (EPSG:27700)</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
@@ -4534,12 +4534,12 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>longitude</t>
+          <t>latitude</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>Longitude</t>
+          <t>Latitude</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr"/>
@@ -4548,12 +4548,12 @@
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>Longitude coordinate in WGS84 (EPSG:4326)</t>
+          <t>Latitude coordinate in WGS84 (EPSG:4326)</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>latitude</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>longitude</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Longitude</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr"/>
@@ -4596,12 +4596,12 @@
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>A text description providing details about the subject. For parking changes, this describes how the proposed works affect existing car parking arrangements.</t>
+          <t>Longitude coordinate in WGS84 (EPSG:4326)</t>
         </is>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>longitude</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
@@ -4630,12 +4630,12 @@
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>uprns</t>
+          <t>description</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>UPRNs[]</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr"/>
@@ -4644,7 +4644,7 @@
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>Unique Property Reference Numbers (UPRNs) for properties within the site boundary</t>
+          <t>A text description providing details about the subject.</t>
         </is>
       </c>
       <c r="M84" s="2" t="inlineStr">
@@ -4659,56 +4659,64 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="2" t="inlineStr">
-        <is>
-          <t>Site Visit Details</t>
-        </is>
-      </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>site-visit</t>
-        </is>
-      </c>
+      <c r="A85" s="2" t="n"/>
+      <c r="B85" s="2" t="n"/>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>Information to help the planning authority arrange a site visit</t>
+          <t>Where the proposed development will be built.</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>can-be-seen-from</t>
+          <t>site-locations</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>Site seen from public area</t>
-        </is>
-      </c>
-      <c r="F85" s="2" t="inlineStr"/>
-      <c r="G85" s="2" t="inlineStr"/>
+          <t>Site locations[]</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>uprns</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>UPRNs[]</t>
+        </is>
+      </c>
       <c r="H85" s="2" t="inlineStr"/>
       <c r="I85" s="2" t="inlineStr"/>
       <c r="J85" s="2" t="inlineStr"/>
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>Can site be seen from a public road, public footpath, bridleway or other public land</t>
+          <t>Unique Property Reference Numbers (UPRNs) for properties within the site boundary</t>
         </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="2" t="n"/>
-      <c r="B86" s="2" t="n"/>
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>Site Visit Details</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>site-visit</t>
+        </is>
+      </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
           <t>Information to help the planning authority arrange a site visit</t>
@@ -4716,12 +4724,12 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>contact-type</t>
+          <t>can-be-seen-from</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Site visit contact type</t>
+          <t>Site seen from public area</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr"/>
@@ -4732,12 +4740,12 @@
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>Indicates who the authority should contact to arrange a site visit</t>
+          <t>Can site be seen from a public road, public footpath, bridleway or other public land</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -4756,12 +4764,12 @@
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>contact-reference</t>
+          <t>contact-type</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>Contact reference</t>
+          <t>Site visit contact type</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr"/>
@@ -4772,17 +4780,17 @@
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>The reference of the applicant or agent who should be contacted for site visits</t>
+          <t>Indicates who the authority should contact to arrange a site visit</t>
         </is>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4796,31 +4804,23 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>other-contact</t>
+          <t>contact-reference</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>Other site visit contact</t>
-        </is>
-      </c>
-      <c r="F88" s="2" t="inlineStr">
-        <is>
-          <t>fullname</t>
-        </is>
-      </c>
-      <c r="G88" s="2" t="inlineStr">
-        <is>
-          <t>Full name</t>
-        </is>
-      </c>
+          <t>Contact reference</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr"/>
+      <c r="G88" s="2" t="inlineStr"/>
       <c r="H88" s="2" t="inlineStr"/>
       <c r="I88" s="2" t="inlineStr"/>
       <c r="J88" s="2" t="inlineStr"/>
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>The complete name of a person</t>
+          <t>The reference of the applicant or agent who should be contacted for site visits</t>
         </is>
       </c>
       <c r="M88" s="2" t="inlineStr">
@@ -4830,7 +4830,7 @@
       </c>
       <c r="N88" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>fullname</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>Phone number</t>
+          <t>Full name</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr"/>
@@ -4868,7 +4868,7 @@
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>The complete name of a person</t>
         </is>
       </c>
       <c r="M89" s="2" t="inlineStr">
@@ -4902,12 +4902,12 @@
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>number</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Phone number</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr"/>
@@ -4916,15 +4916,63 @@
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr">
         <is>
+          <t>A phone number</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="n"/>
+      <c r="B91" s="2" t="n"/>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>Information to help the planning authority arrange a site visit</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>other-contact</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>Other site visit contact</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr"/>
+      <c r="I91" s="2" t="inlineStr"/>
+      <c r="J91" s="2" t="inlineStr"/>
+      <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
           <t>The email address that can be used for electronic correspondence with the individual</t>
         </is>
       </c>
-      <c r="M90" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="N90" s="2" t="inlineStr">
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N91" s="2" t="inlineStr">
         <is>
           <t>MUST</t>
         </is>
@@ -4932,34 +4980,34 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B35:B40"/>
-    <mergeCell ref="B31:B34"/>
-    <mergeCell ref="B43:B44"/>
-    <mergeCell ref="B56:B70"/>
-    <mergeCell ref="A48:A55"/>
-    <mergeCell ref="A71:A75"/>
-    <mergeCell ref="B41"/>
-    <mergeCell ref="B2:B18"/>
-    <mergeCell ref="A76:A84"/>
-    <mergeCell ref="B45:B47"/>
-    <mergeCell ref="B19:B22"/>
-    <mergeCell ref="A56:A70"/>
-    <mergeCell ref="B23:B30"/>
-    <mergeCell ref="A45:A47"/>
-    <mergeCell ref="B48:B55"/>
-    <mergeCell ref="B71:B75"/>
-    <mergeCell ref="A2:A18"/>
-    <mergeCell ref="B76:B84"/>
-    <mergeCell ref="A85:A90"/>
+    <mergeCell ref="A43"/>
+    <mergeCell ref="A2:A19"/>
+    <mergeCell ref="A24:A31"/>
+    <mergeCell ref="A49:A56"/>
+    <mergeCell ref="A36:A41"/>
+    <mergeCell ref="A72:A76"/>
+    <mergeCell ref="B57:B71"/>
+    <mergeCell ref="B86:B91"/>
+    <mergeCell ref="B72:B76"/>
+    <mergeCell ref="B44:B45"/>
+    <mergeCell ref="A32:A35"/>
+    <mergeCell ref="B43"/>
+    <mergeCell ref="A57:A71"/>
+    <mergeCell ref="A86:A91"/>
+    <mergeCell ref="A20:A23"/>
+    <mergeCell ref="A77:A85"/>
+    <mergeCell ref="B46:B48"/>
     <mergeCell ref="B42"/>
-    <mergeCell ref="A41"/>
-    <mergeCell ref="A19:A22"/>
-    <mergeCell ref="A43:A44"/>
-    <mergeCell ref="A35:A40"/>
-    <mergeCell ref="A31:A34"/>
-    <mergeCell ref="A23:A30"/>
+    <mergeCell ref="A44:A45"/>
+    <mergeCell ref="B36:B41"/>
+    <mergeCell ref="B49:B56"/>
+    <mergeCell ref="B20:B23"/>
+    <mergeCell ref="B2:B19"/>
+    <mergeCell ref="B24:B31"/>
     <mergeCell ref="A42"/>
-    <mergeCell ref="B85:B90"/>
+    <mergeCell ref="A46:A48"/>
+    <mergeCell ref="B77:B85"/>
+    <mergeCell ref="B32:B35"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/generated/spreadsheet/verbose/removal-or-variation-of-a-condition-following-grant-of-planning-permission-s73-verbose.xlsx
+++ b/generated/spreadsheet/verbose/removal-or-variation-of-a-condition-following-grant-of-planning-permission-s73-verbose.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N91"/>
+  <dimension ref="A1:N94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
@@ -440,9 +440,9 @@
     <col width="18" customWidth="1" min="8" max="8"/>
     <col width="18" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
     <col width="72" customWidth="1" min="12" max="12"/>
-    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
     <col width="13" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
@@ -1980,19 +1980,27 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
+          <t>contact-address</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>address-text</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr">
+      <c r="K28" s="2" t="inlineStr">
         <is>
           <t>Address Text</t>
         </is>
       </c>
-      <c r="J28" s="2" t="inlineStr"/>
-      <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>Text representation of an address or site</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
@@ -2036,19 +2044,27 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
+          <t>contact-address</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>postcode</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr">
+      <c r="K29" s="2" t="inlineStr">
         <is>
           <t>Postcode</t>
         </is>
       </c>
-      <c r="J29" s="2" t="inlineStr"/>
-      <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>Postcode for a contact address or site</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
@@ -2082,21 +2098,37 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>company</t>
+          <t>person</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Company</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr"/>
-      <c r="I30" s="2" t="inlineStr"/>
-      <c r="J30" s="2" t="inlineStr"/>
-      <c r="K30" s="2" t="inlineStr"/>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>contact-address</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>uprn</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>UPRN</t>
+        </is>
+      </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>The name of a company (that the agent works for)</t>
+          <t>Unique Property Reference Number for a property</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
@@ -2130,12 +2162,12 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>user-role</t>
+          <t>company</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>User role</t>
+          <t>Company</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr"/>
@@ -2144,12 +2176,12 @@
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>The role of the named individual. Agent or proxy</t>
+          <t>The name of a company (that the agent works for)</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -2159,56 +2191,64 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>Applicant contact details</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>applicant-contact</t>
-        </is>
-      </c>
+      <c r="A32" s="2" t="n"/>
+      <c r="B32" s="2" t="n"/>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Telephone number and email address of the applicant.</t>
+          <t>Name and contact information if an agent is being used.</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>applicant-reference</t>
+          <t>agent</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Applicant reference</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr"/>
-      <c r="G32" s="2" t="inlineStr"/>
+          <t>agent</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>user-role</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>User role</t>
+        </is>
+      </c>
       <c r="H32" s="2" t="inlineStr"/>
       <c r="I32" s="2" t="inlineStr"/>
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>Reference to match contact details to a named individual from the applicant details component</t>
+          <t>The role of the named individual. Agent or proxy</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="n"/>
-      <c r="B33" s="2" t="n"/>
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>Applicant contact details</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>applicant-contact</t>
+        </is>
+      </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
           <t>Telephone number and email address of the applicant.</t>
@@ -2216,31 +2256,23 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>contact-details</t>
+          <t>applicant-reference</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Contact details</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
+          <t>Applicant reference</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr"/>
+      <c r="G33" s="2" t="inlineStr"/>
       <c r="H33" s="2" t="inlineStr"/>
       <c r="I33" s="2" t="inlineStr"/>
       <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>The email address that can be used for electronic correspondence with the individual</t>
+          <t>Reference to match contact details to a named individual from the applicant details component</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
@@ -2274,29 +2306,21 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>phone-numbers</t>
+          <t>email</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Phone number(s)[]</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>number</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>Phone number</t>
-        </is>
-      </c>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr"/>
+      <c r="I34" s="2" t="inlineStr"/>
       <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>The email address that can be used for electronic correspondence with the individual</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
@@ -2306,7 +2330,7 @@
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2340,24 +2364,24 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>contact-priority</t>
+          <t>number</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>Contact priority</t>
+          <t>Phone number</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>The priority of a number</t>
+          <t>A phone number</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -2367,64 +2391,72 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>Applicant details</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>applicant-details</t>
-        </is>
-      </c>
+      <c r="A36" s="2" t="n"/>
+      <c r="B36" s="2" t="n"/>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Name and contact information for the parties making the application.</t>
+          <t>Telephone number and email address of the applicant.</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>applicants</t>
+          <t>contact-details</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Applicants[]</t>
+          <t>Contact details</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>reference</t>
+          <t>phone-numbers</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr"/>
-      <c r="I36" s="2" t="inlineStr"/>
+          <t>Phone number(s)[]</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>contact-priority</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>Contact priority</t>
+        </is>
+      </c>
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>The priority of a number</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="n"/>
-      <c r="B37" s="2" t="n"/>
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>Applicant details</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>applicant-details</t>
+        </is>
+      </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
           <t>Name and contact information for the parties making the application.</t>
@@ -2442,29 +2474,21 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>person</t>
+          <t>reference</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr"/>
+      <c r="I37" s="2" t="inlineStr"/>
       <c r="J37" s="2" t="inlineStr"/>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>The title of the individual</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
@@ -2474,7 +2498,7 @@
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2508,19 +2532,19 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>first-name</t>
+          <t>title</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>First Name</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>The first name of the individual</t>
+          <t>The title of the individual</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
@@ -2530,7 +2554,7 @@
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2564,19 +2588,19 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>last-name</t>
+          <t>first-name</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>The last name of the individual</t>
+          <t>The first name of the individual</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
@@ -2620,19 +2644,19 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>address-text</t>
+          <t>last-name</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The last name of the individual</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
@@ -2676,132 +2700,192 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
+          <t>contact-address</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>address-text</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>Address Text</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>Text representation of an address or site</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="n"/>
+      <c r="B42" s="2" t="n"/>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Name and contact information for the parties making the application.</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>applicants</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>Applicants[]</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>contact-address</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
           <t>postcode</t>
         </is>
       </c>
-      <c r="I41" s="2" t="inlineStr">
+      <c r="K42" s="2" t="inlineStr">
         <is>
           <t>Postcode</t>
         </is>
       </c>
-      <c r="J41" s="2" t="inlineStr"/>
-      <c r="K41" s="2" t="inlineStr"/>
-      <c r="L41" s="2" t="inlineStr">
-        <is>
-          <t>The postal code</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="N41" s="2" t="inlineStr">
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>Postcode for a contact address or site</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
         <is>
           <t>MAY</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>Checklist</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>checklist</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>Checking whether all the requirements of the form have been met, such as proof of payment or supporting documentation.</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>national-req-types</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>National requirement types[]</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr"/>
-      <c r="G42" s="2" t="inlineStr"/>
-      <c r="H42" s="2" t="inlineStr"/>
-      <c r="I42" s="2" t="inlineStr"/>
-      <c r="J42" s="2" t="inlineStr"/>
-      <c r="K42" s="2" t="inlineStr"/>
-      <c r="L42" s="2" t="inlineStr">
-        <is>
-          <t>List of the document types required for the given application type</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="N42" s="2" t="inlineStr">
-        <is>
-          <t>MUST</t>
-        </is>
-      </c>
-    </row>
     <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>Conflict of interest</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>conflict-of-interest</t>
-        </is>
-      </c>
+      <c r="A43" s="2" t="n"/>
+      <c r="B43" s="2" t="n"/>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Details of any conflict of interest that may exist between the applicant and planning authority.</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr"/>
-      <c r="E43" s="2" t="inlineStr"/>
-      <c r="F43" s="2" t="inlineStr"/>
-      <c r="G43" s="2" t="inlineStr"/>
-      <c r="H43" s="2" t="inlineStr"/>
-      <c r="I43" s="2" t="inlineStr"/>
-      <c r="J43" s="2" t="inlineStr"/>
-      <c r="K43" s="2" t="inlineStr"/>
-      <c r="L43" s="2" t="inlineStr"/>
-      <c r="M43" s="2" t="inlineStr"/>
-      <c r="N43" s="2" t="inlineStr"/>
+          <t>Name and contact information for the parties making the application.</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>applicants</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>Applicants[]</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>contact-address</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>uprn</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>UPRN</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>Unique Property Reference Number for a property</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>MAY</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>Condition removal or variation</t>
+          <t>Checklist</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>con-remove-vary</t>
+          <t>checklist</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Why the applicant is asking for planning conditions to be removed or changed.</t>
+          <t>Checking whether all the requirements of the form have been met, such as proof of payment or supporting documentation.</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>reason</t>
+          <t>national-req-types</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Reason</t>
+          <t>National requirement types[]</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr"/>
@@ -2812,7 +2896,7 @@
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>The reason why the applicant wishes condition(s) to be removed or changed</t>
+          <t>List of the document types required for the given application type</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
@@ -2827,69 +2911,57 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="n"/>
-      <c r="B45" s="2" t="n"/>
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>Conflict of interest</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>conflict-of-interest</t>
+        </is>
+      </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Why the applicant is asking for planning conditions to be removed or changed.</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>condition-change</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>Condition change</t>
-        </is>
-      </c>
+          <t>Details of any conflict of interest that may exist between the applicant and planning authority.</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr"/>
+      <c r="E45" s="2" t="inlineStr"/>
       <c r="F45" s="2" t="inlineStr"/>
       <c r="G45" s="2" t="inlineStr"/>
       <c r="H45" s="2" t="inlineStr"/>
       <c r="I45" s="2" t="inlineStr"/>
       <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="2" t="inlineStr"/>
-      <c r="L45" s="2" t="inlineStr">
-        <is>
-          <t>State how the condition should vary</t>
-        </is>
-      </c>
-      <c r="M45" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="N45" s="2" t="inlineStr">
-        <is>
-          <t>MAY</t>
-        </is>
-      </c>
+      <c r="L45" s="2" t="inlineStr"/>
+      <c r="M45" s="2" t="inlineStr"/>
+      <c r="N45" s="2" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>Declaration</t>
+          <t>Condition removal or variation</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>declaration</t>
+          <t>con-remove-vary</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Signed and dated verification of the application's accuracy.</t>
+          <t>Why the applicant is asking for planning conditions to be removed or changed.</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>person-reference</t>
+          <t>reason</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Person reference</t>
+          <t>Reason</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr"/>
@@ -2900,7 +2972,7 @@
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>Declaration must be made by an applicant or agent making the application</t>
+          <t>The reason why the applicant wishes condition(s) to be removed or changed</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
@@ -2919,17 +2991,17 @@
       <c r="B47" s="2" t="n"/>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Signed and dated verification of the application's accuracy.</t>
+          <t>Why the applicant is asking for planning conditions to be removed or changed.</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>declaration-confirmed</t>
+          <t>condition-change</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>Declaration confirmed</t>
+          <t>Condition change</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr"/>
@@ -2940,23 +3012,31 @@
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
+          <t>State how the condition should vary</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="n"/>
-      <c r="B48" s="2" t="n"/>
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>Declaration</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>declaration</t>
+        </is>
+      </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
           <t>Signed and dated verification of the application's accuracy.</t>
@@ -2964,12 +3044,12 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>declaration-date</t>
+          <t>person-reference</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Declaration date</t>
+          <t>Person reference</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr"/>
@@ -2980,12 +3060,12 @@
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>The date the declaration was made</t>
+          <t>Declaration must be made by an applicant or agent making the application</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -2995,53 +3075,37 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>Description of your proposal</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>desc-your-proposal</t>
-        </is>
-      </c>
+      <c r="A49" s="2" t="n"/>
+      <c r="B49" s="2" t="n"/>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Written description of the proposed development including any additional relevant details.</t>
+          <t>Signed and dated verification of the application's accuracy.</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>related-application</t>
+          <t>declaration-confirmed</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>Related application</t>
-        </is>
-      </c>
-      <c r="F49" s="2" t="inlineStr">
-        <is>
-          <t>reference</t>
-        </is>
-      </c>
-      <c r="G49" s="2" t="inlineStr">
-        <is>
-          <t>Reference</t>
-        </is>
-      </c>
+          <t>Declaration confirmed</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr"/>
+      <c r="G49" s="2" t="inlineStr"/>
       <c r="H49" s="2" t="inlineStr"/>
       <c r="I49" s="2" t="inlineStr"/>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>The reference for the related application</t>
+          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -3055,41 +3119,33 @@
       <c r="B50" s="2" t="n"/>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Written description of the proposed development including any additional relevant details.</t>
+          <t>Signed and dated verification of the application's accuracy.</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>related-application</t>
+          <t>declaration-date</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Related application</t>
-        </is>
-      </c>
-      <c r="F50" s="2" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="G50" s="2" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
+          <t>Declaration date</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr"/>
+      <c r="G50" s="2" t="inlineStr"/>
       <c r="H50" s="2" t="inlineStr"/>
       <c r="I50" s="2" t="inlineStr"/>
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>A description of the related application</t>
+          <t>The date the declaration was made</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -3099,8 +3155,16 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="n"/>
-      <c r="B51" s="2" t="n"/>
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>Description of your proposal</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>desc-your-proposal</t>
+        </is>
+      </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
           <t>Written description of the proposed development including any additional relevant details.</t>
@@ -3118,12 +3182,12 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>decision-date</t>
+          <t>reference</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>Decision date</t>
+          <t>Reference</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr"/>
@@ -3132,17 +3196,17 @@
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>The date when the decision was made, in YYYY-MM-DD format</t>
+          <t>The reference for the related application</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3156,33 +3220,41 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>condition-numbers</t>
+          <t>related-application</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Condition numbers[]</t>
-        </is>
-      </c>
-      <c r="F52" s="2" t="inlineStr"/>
-      <c r="G52" s="2" t="inlineStr"/>
+          <t>Related application</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
       <c r="H52" s="2" t="inlineStr"/>
       <c r="I52" s="2" t="inlineStr"/>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>List of condition numbers related to this application</t>
+          <t>A description of the related application</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3196,33 +3268,41 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>has-development-started</t>
+          <t>related-application</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>Has development started</t>
-        </is>
-      </c>
-      <c r="F53" s="2" t="inlineStr"/>
-      <c r="G53" s="2" t="inlineStr"/>
+          <t>Related application</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>decision-date</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>Decision date</t>
+        </is>
+      </c>
       <c r="H53" s="2" t="inlineStr"/>
       <c r="I53" s="2" t="inlineStr"/>
       <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>Whether the development has already started</t>
+          <t>The date when the decision was made, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3236,12 +3316,12 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>development-start-date</t>
+          <t>condition-numbers</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Development start date</t>
+          <t>Condition numbers[]</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr"/>
@@ -3252,12 +3332,12 @@
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>Date when development started</t>
+          <t>List of condition numbers related to this application</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -3276,12 +3356,12 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>has-development-completed</t>
+          <t>has-development-started</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>Has development completed</t>
+          <t>Has development started</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr"/>
@@ -3292,7 +3372,7 @@
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>Whether the development has been completed</t>
+          <t>Whether the development has already started</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
@@ -3316,12 +3396,12 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>development-completed-date</t>
+          <t>development-start-date</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Development completed date</t>
+          <t>Development start date</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr"/>
@@ -3332,7 +3412,7 @@
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>Date when development was completed</t>
+          <t>Date when development started</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
@@ -3347,29 +3427,21 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>Ownership certificates and agricultural land declaration</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>ownership-certs</t>
-        </is>
-      </c>
+      <c r="A57" s="2" t="n"/>
+      <c r="B57" s="2" t="n"/>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Who will be affected by the proposal and whether they have been notified, such as agricultural tenants</t>
+          <t>Written description of the proposed development including any additional relevant details.</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>sole-owner</t>
+          <t>has-development-completed</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>Sole owner</t>
+          <t>Has development completed</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr"/>
@@ -3380,7 +3452,7 @@
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>Is the applicant the sole owner of the land?</t>
+          <t>Whether the development has been completed</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
@@ -3399,17 +3471,17 @@
       <c r="B58" s="2" t="n"/>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Who will be affected by the proposal and whether they have been notified, such as agricultural tenants</t>
+          <t>Written description of the proposed development including any additional relevant details.</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>agricultural-tenants</t>
+          <t>development-completed-date</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Agricultural tenants</t>
+          <t>Development completed date</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr"/>
@@ -3420,23 +3492,31 @@
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>Are there any agricultural tenants on the land?</t>
+          <t>Date when development was completed</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="n"/>
-      <c r="B59" s="2" t="n"/>
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>Ownership certificates and agricultural land declaration</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>ownership-certs</t>
+        </is>
+      </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
           <t>Who will be affected by the proposal and whether they have been notified, such as agricultural tenants</t>
@@ -3444,49 +3524,33 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>owners-and-tenants</t>
+          <t>sole-owner</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>Owners and tenants[]</t>
-        </is>
-      </c>
-      <c r="F59" s="2" t="inlineStr">
-        <is>
-          <t>person</t>
-        </is>
-      </c>
-      <c r="G59" s="2" t="inlineStr">
-        <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="H59" s="2" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="I59" s="2" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
+          <t>Sole owner</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr"/>
+      <c r="G59" s="2" t="inlineStr"/>
+      <c r="H59" s="2" t="inlineStr"/>
+      <c r="I59" s="2" t="inlineStr"/>
       <c r="J59" s="2" t="inlineStr"/>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>The title of the individual</t>
+          <t>Is the applicant the sole owner of the land?</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3500,44 +3564,28 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>owners-and-tenants</t>
+          <t>agricultural-tenants</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Owners and tenants[]</t>
-        </is>
-      </c>
-      <c r="F60" s="2" t="inlineStr">
-        <is>
-          <t>person</t>
-        </is>
-      </c>
-      <c r="G60" s="2" t="inlineStr">
-        <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="H60" s="2" t="inlineStr">
-        <is>
-          <t>first-name</t>
-        </is>
-      </c>
-      <c r="I60" s="2" t="inlineStr">
-        <is>
-          <t>First Name</t>
-        </is>
-      </c>
+          <t>Agricultural tenants</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr"/>
+      <c r="G60" s="2" t="inlineStr"/>
+      <c r="H60" s="2" t="inlineStr"/>
+      <c r="I60" s="2" t="inlineStr"/>
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>The first name of the individual</t>
+          <t>Are there any agricultural tenants on the land?</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -3576,19 +3624,19 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>last-name</t>
+          <t>title</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr"/>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>The last name of the individual</t>
+          <t>The title of the individual</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
@@ -3598,7 +3646,7 @@
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3632,19 +3680,19 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>address-text</t>
+          <t>first-name</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The first name of the individual</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
@@ -3688,19 +3736,19 @@
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>postcode</t>
+          <t>last-name</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>Postcode</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>The last name of the individual</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
@@ -3710,7 +3758,7 @@
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3734,31 +3782,47 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>notice-served-date</t>
+          <t>person</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>Notice served date</t>
-        </is>
-      </c>
-      <c r="H64" s="2" t="inlineStr"/>
-      <c r="I64" s="2" t="inlineStr"/>
-      <c r="J64" s="2" t="inlineStr"/>
-      <c r="K64" s="2" t="inlineStr"/>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>contact-address</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>address-text</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr">
+        <is>
+          <t>Address Text</t>
+        </is>
+      </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>Date when notice was served</t>
+          <t>Text representation of an address or site</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3772,28 +3836,52 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>ownership-cert-option</t>
+          <t>owners-and-tenants</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>Ownership certificate type</t>
-        </is>
-      </c>
-      <c r="F65" s="2" t="inlineStr"/>
-      <c r="G65" s="2" t="inlineStr"/>
-      <c r="H65" s="2" t="inlineStr"/>
-      <c r="I65" s="2" t="inlineStr"/>
-      <c r="J65" s="2" t="inlineStr"/>
-      <c r="K65" s="2" t="inlineStr"/>
+          <t>Owners and tenants[]</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>contact-address</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>postcode</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="inlineStr">
+        <is>
+          <t>Postcode</t>
+        </is>
+      </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>The type of ownership certificate based on ownership and tenancy status</t>
+          <t>Postcode for a contact address or site</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -3812,23 +3900,47 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>steps-taken</t>
+          <t>owners-and-tenants</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Steps taken</t>
-        </is>
-      </c>
-      <c r="F66" s="2" t="inlineStr"/>
-      <c r="G66" s="2" t="inlineStr"/>
-      <c r="H66" s="2" t="inlineStr"/>
-      <c r="I66" s="2" t="inlineStr"/>
-      <c r="J66" s="2" t="inlineStr"/>
-      <c r="K66" s="2" t="inlineStr"/>
+          <t>Owners and tenants[]</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>contact-address</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>uprn</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr">
+        <is>
+          <t>UPRN</t>
+        </is>
+      </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>Description of steps taken to identify unknown owners or tenants</t>
+          <t>Unique Property Reference Number for a property</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
@@ -3852,22 +3964,22 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>newspaper-notices</t>
+          <t>owners-and-tenants</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>Newspaper notices[]</t>
+          <t>Owners and tenants[]</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>newspaper-name</t>
+          <t>notice-served-date</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>Newspaper name</t>
+          <t>Notice served date</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr"/>
@@ -3876,17 +3988,17 @@
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>Name of the newspaper where notice was published</t>
+          <t>Date when notice was served</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3900,41 +4012,33 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>newspaper-notices</t>
+          <t>ownership-cert-option</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Newspaper notices[]</t>
-        </is>
-      </c>
-      <c r="F68" s="2" t="inlineStr">
-        <is>
-          <t>publication-date</t>
-        </is>
-      </c>
-      <c r="G68" s="2" t="inlineStr">
-        <is>
-          <t>Publication date</t>
-        </is>
-      </c>
+          <t>Ownership certificate type</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr"/>
+      <c r="G68" s="2" t="inlineStr"/>
       <c r="H68" s="2" t="inlineStr"/>
       <c r="I68" s="2" t="inlineStr"/>
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>Date when the notice was published</t>
+          <t>The type of ownership certificate based on ownership and tenancy status</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3948,12 +4052,12 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>person-reference</t>
+          <t>steps-taken</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>Person reference</t>
+          <t>Steps taken</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr"/>
@@ -3964,7 +4068,7 @@
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>Declaration must be made by an applicant or agent making the application</t>
+          <t>Description of steps taken to identify unknown owners or tenants</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
@@ -3974,7 +4078,7 @@
       </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3988,28 +4092,36 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>declaration-confirmed</t>
+          <t>newspaper-notices</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Declaration confirmed</t>
-        </is>
-      </c>
-      <c r="F70" s="2" t="inlineStr"/>
-      <c r="G70" s="2" t="inlineStr"/>
+          <t>Newspaper notices[]</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>newspaper-name</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>Newspaper name</t>
+        </is>
+      </c>
       <c r="H70" s="2" t="inlineStr"/>
       <c r="I70" s="2" t="inlineStr"/>
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
+          <t>Name of the newspaper where notice was published</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -4028,23 +4140,31 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>declaration-date</t>
+          <t>newspaper-notices</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>Declaration date</t>
-        </is>
-      </c>
-      <c r="F71" s="2" t="inlineStr"/>
-      <c r="G71" s="2" t="inlineStr"/>
+          <t>Newspaper notices[]</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>publication-date</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>Publication date</t>
+        </is>
+      </c>
       <c r="H71" s="2" t="inlineStr"/>
       <c r="I71" s="2" t="inlineStr"/>
       <c r="J71" s="2" t="inlineStr"/>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>The date the declaration was made</t>
+          <t>Date when the notice was published</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
@@ -4059,29 +4179,21 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="2" t="inlineStr">
-        <is>
-          <t>Pre-application advice</t>
-        </is>
-      </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>pre-app-advice</t>
-        </is>
-      </c>
+      <c r="A72" s="2" t="n"/>
+      <c r="B72" s="2" t="n"/>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Details of pre-application advice previously received from the planning authority</t>
+          <t>Who will be affected by the proposal and whether they have been notified, such as agricultural tenants</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>advice-sought</t>
+          <t>person-reference</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Pre-application advice sought</t>
+          <t>Person reference</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr"/>
@@ -4092,12 +4204,12 @@
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>Whether pre-application advice has been sought from the planning authority</t>
+          <t>Declaration must be made by an applicant or agent making the application</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -4111,17 +4223,17 @@
       <c r="B73" s="2" t="n"/>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>Details of pre-application advice previously received from the planning authority</t>
+          <t>Who will be affected by the proposal and whether they have been notified, such as agricultural tenants</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>officer-name</t>
+          <t>declaration-confirmed</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>Officer name</t>
+          <t>Declaration confirmed</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr"/>
@@ -4132,17 +4244,17 @@
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>Name of the planning officer who provided the pre-application advice</t>
+          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4151,17 +4263,17 @@
       <c r="B74" s="2" t="n"/>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Details of pre-application advice previously received from the planning authority</t>
+          <t>Who will be affected by the proposal and whether they have been notified, such as agricultural tenants</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>reference</t>
+          <t>declaration-date</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
+          <t>Declaration date</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr"/>
@@ -4172,23 +4284,31 @@
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>The date the declaration was made</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="2" t="n"/>
-      <c r="B75" s="2" t="n"/>
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>Pre-application advice</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>pre-app-advice</t>
+        </is>
+      </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
           <t>Details of pre-application advice previously received from the planning authority</t>
@@ -4196,12 +4316,12 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>advice-date</t>
+          <t>advice-sought</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>Advice date</t>
+          <t>Pre-application advice sought</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr"/>
@@ -4212,17 +4332,17 @@
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>Date when pre-application advice was received, in YYYY-MM-DD format</t>
+          <t>Whether pre-application advice has been sought from the planning authority</t>
         </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4236,12 +4356,12 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>advice-summary</t>
+          <t>officer-name</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Advice summary</t>
+          <t>Officer name</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr"/>
@@ -4252,7 +4372,7 @@
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>Summary of the pre-application advice received from the planning authority</t>
+          <t>Name of the planning officer who provided the pre-application advice</t>
         </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
@@ -4267,53 +4387,37 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="inlineStr">
-        <is>
-          <t>Site details</t>
-        </is>
-      </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>site-details</t>
-        </is>
-      </c>
+      <c r="A77" s="2" t="n"/>
+      <c r="B77" s="2" t="n"/>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Where the proposed development will be built.</t>
+          <t>Details of pre-application advice previously received from the planning authority</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>site-locations</t>
+          <t>reference</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>Site locations[]</t>
-        </is>
-      </c>
-      <c r="F77" s="2" t="inlineStr">
-        <is>
-          <t>site-boundary</t>
-        </is>
-      </c>
-      <c r="G77" s="2" t="inlineStr">
-        <is>
-          <t>Site boundary</t>
-        </is>
-      </c>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr"/>
+      <c r="G77" s="2" t="inlineStr"/>
       <c r="H77" s="2" t="inlineStr"/>
       <c r="I77" s="2" t="inlineStr"/>
       <c r="J77" s="2" t="inlineStr"/>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>Geometry of the site of the development, typically in GeoJSON format</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>wkt</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
@@ -4327,41 +4431,33 @@
       <c r="B78" s="2" t="n"/>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Where the proposed development will be built.</t>
+          <t>Details of pre-application advice previously received from the planning authority</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>site-locations</t>
+          <t>advice-date</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Site locations[]</t>
-        </is>
-      </c>
-      <c r="F78" s="2" t="inlineStr">
-        <is>
-          <t>address-text</t>
-        </is>
-      </c>
-      <c r="G78" s="2" t="inlineStr">
-        <is>
-          <t>Address Text</t>
-        </is>
-      </c>
+          <t>Advice date</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr"/>
+      <c r="G78" s="2" t="inlineStr"/>
       <c r="H78" s="2" t="inlineStr"/>
       <c r="I78" s="2" t="inlineStr"/>
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>Date when pre-application advice was received, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -4375,36 +4471,28 @@
       <c r="B79" s="2" t="n"/>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>Where the proposed development will be built.</t>
+          <t>Details of pre-application advice previously received from the planning authority</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>site-locations</t>
+          <t>advice-summary</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>Site locations[]</t>
-        </is>
-      </c>
-      <c r="F79" s="2" t="inlineStr">
-        <is>
-          <t>postcode</t>
-        </is>
-      </c>
-      <c r="G79" s="2" t="inlineStr">
-        <is>
-          <t>Postcode</t>
-        </is>
-      </c>
+          <t>Advice summary</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr"/>
+      <c r="G79" s="2" t="inlineStr"/>
       <c r="H79" s="2" t="inlineStr"/>
       <c r="I79" s="2" t="inlineStr"/>
       <c r="J79" s="2" t="inlineStr"/>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>Summary of the pre-application advice received from the planning authority</t>
         </is>
       </c>
       <c r="M79" s="2" t="inlineStr">
@@ -4419,8 +4507,16 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="2" t="n"/>
-      <c r="B80" s="2" t="n"/>
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>Site details</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>site-details</t>
+        </is>
+      </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
           <t>Where the proposed development will be built.</t>
@@ -4438,12 +4534,12 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>easting</t>
+          <t>geometry</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>Easting</t>
+          <t>Site boundary</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr"/>
@@ -4452,17 +4548,17 @@
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>Easting coordinate in British National Grid (EPSG:27700)</t>
+          <t>A polygon or multipolygon boundary</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>multipolygon</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4486,31 +4582,39 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>northing</t>
+          <t>site-address</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>Northing</t>
-        </is>
-      </c>
-      <c r="H81" s="2" t="inlineStr"/>
-      <c r="I81" s="2" t="inlineStr"/>
+          <t>Site address</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>address-text</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>Address Text</t>
+        </is>
+      </c>
       <c r="J81" s="2" t="inlineStr"/>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>Northing coordinate in British National Grid (EPSG:27700)</t>
+          <t>Text representation of an address or site</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4534,26 +4638,34 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>latitude</t>
+          <t>site-address</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>Latitude</t>
-        </is>
-      </c>
-      <c r="H82" s="2" t="inlineStr"/>
-      <c r="I82" s="2" t="inlineStr"/>
+          <t>Site address</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>postcode</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>Postcode</t>
+        </is>
+      </c>
       <c r="J82" s="2" t="inlineStr"/>
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>Latitude coordinate in WGS84 (EPSG:4326)</t>
+          <t>Postcode for a contact address or site</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>latitude</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -4582,26 +4694,34 @@
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>longitude</t>
+          <t>site-address</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>Longitude</t>
-        </is>
-      </c>
-      <c r="H83" s="2" t="inlineStr"/>
-      <c r="I83" s="2" t="inlineStr"/>
+          <t>Site address</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>uprns</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>UPRNs[]</t>
+        </is>
+      </c>
       <c r="J83" s="2" t="inlineStr"/>
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>Longitude coordinate in WGS84 (EPSG:4326)</t>
+          <t>Unique Property Reference Numbers (UPRNs) for existing premises within a site boundary</t>
         </is>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>longitude</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
@@ -4630,21 +4750,29 @@
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>site-address</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="H84" s="2" t="inlineStr"/>
-      <c r="I84" s="2" t="inlineStr"/>
+          <t>Site address</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>usrns</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>USRNs[]</t>
+        </is>
+      </c>
       <c r="J84" s="2" t="inlineStr"/>
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>A text description providing details about the subject.</t>
+          <t>Unique Street Reference Numbers (USRNs) associated with the site</t>
         </is>
       </c>
       <c r="M84" s="2" t="inlineStr">
@@ -4678,12 +4806,12 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>uprns</t>
+          <t>easting</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>UPRNs[]</t>
+          <t>Easting</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr"/>
@@ -4692,12 +4820,12 @@
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>Unique Property Reference Numbers (UPRNs) for properties within the site boundary</t>
+          <t>Easting coordinate in British National Grid (EPSG:27700)</t>
         </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
@@ -4707,50 +4835,50 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="2" t="inlineStr">
-        <is>
-          <t>Site Visit Details</t>
-        </is>
-      </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>site-visit</t>
-        </is>
-      </c>
+      <c r="A86" s="2" t="n"/>
+      <c r="B86" s="2" t="n"/>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>Information to help the planning authority arrange a site visit</t>
+          <t>Where the proposed development will be built.</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>can-be-seen-from</t>
+          <t>site-locations</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Site seen from public area</t>
-        </is>
-      </c>
-      <c r="F86" s="2" t="inlineStr"/>
-      <c r="G86" s="2" t="inlineStr"/>
+          <t>Site locations[]</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>northing</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>Northing</t>
+        </is>
+      </c>
       <c r="H86" s="2" t="inlineStr"/>
       <c r="I86" s="2" t="inlineStr"/>
       <c r="J86" s="2" t="inlineStr"/>
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>Can site be seen from a public road, public footpath, bridleway or other public land</t>
+          <t>Northing coordinate in British National Grid (EPSG:27700)</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4759,38 +4887,46 @@
       <c r="B87" s="2" t="n"/>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>Information to help the planning authority arrange a site visit</t>
+          <t>Where the proposed development will be built.</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>contact-type</t>
+          <t>site-locations</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>Site visit contact type</t>
-        </is>
-      </c>
-      <c r="F87" s="2" t="inlineStr"/>
-      <c r="G87" s="2" t="inlineStr"/>
+          <t>Site locations[]</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>latitude</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>Latitude</t>
+        </is>
+      </c>
       <c r="H87" s="2" t="inlineStr"/>
       <c r="I87" s="2" t="inlineStr"/>
       <c r="J87" s="2" t="inlineStr"/>
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>Indicates who the authority should contact to arrange a site visit</t>
+          <t>Latitude coordinate in WGS84 (EPSG:4326)</t>
         </is>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>latitude</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4799,33 +4935,41 @@
       <c r="B88" s="2" t="n"/>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>Information to help the planning authority arrange a site visit</t>
+          <t>Where the proposed development will be built.</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>contact-reference</t>
+          <t>site-locations</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>Contact reference</t>
-        </is>
-      </c>
-      <c r="F88" s="2" t="inlineStr"/>
-      <c r="G88" s="2" t="inlineStr"/>
+          <t>Site locations[]</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>longitude</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>Longitude</t>
+        </is>
+      </c>
       <c r="H88" s="2" t="inlineStr"/>
       <c r="I88" s="2" t="inlineStr"/>
       <c r="J88" s="2" t="inlineStr"/>
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>The reference of the applicant or agent who should be contacted for site visits</t>
+          <t>Longitude coordinate in WGS84 (EPSG:4326)</t>
         </is>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>longitude</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
@@ -4835,8 +4979,16 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="2" t="n"/>
-      <c r="B89" s="2" t="n"/>
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>Site Visit Details</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>site-visit</t>
+        </is>
+      </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
           <t>Information to help the planning authority arrange a site visit</t>
@@ -4844,36 +4996,28 @@
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>other-contact</t>
+          <t>can-be-seen-from</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>Other site visit contact</t>
-        </is>
-      </c>
-      <c r="F89" s="2" t="inlineStr">
-        <is>
-          <t>fullname</t>
-        </is>
-      </c>
-      <c r="G89" s="2" t="inlineStr">
-        <is>
-          <t>Full name</t>
-        </is>
-      </c>
+          <t>Site seen from public area</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr"/>
+      <c r="G89" s="2" t="inlineStr"/>
       <c r="H89" s="2" t="inlineStr"/>
       <c r="I89" s="2" t="inlineStr"/>
       <c r="J89" s="2" t="inlineStr"/>
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>The complete name of a person</t>
+          <t>Can site be seen from a public road, public footpath, bridleway or other public land</t>
         </is>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
@@ -4892,36 +5036,28 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>other-contact</t>
+          <t>contact-type</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>Other site visit contact</t>
-        </is>
-      </c>
-      <c r="F90" s="2" t="inlineStr">
-        <is>
-          <t>number</t>
-        </is>
-      </c>
-      <c r="G90" s="2" t="inlineStr">
-        <is>
-          <t>Phone number</t>
-        </is>
-      </c>
+          <t>Site visit contact type</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr"/>
+      <c r="G90" s="2" t="inlineStr"/>
       <c r="H90" s="2" t="inlineStr"/>
       <c r="I90" s="2" t="inlineStr"/>
       <c r="J90" s="2" t="inlineStr"/>
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>Indicates who the authority should contact to arrange a site visit</t>
         </is>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
@@ -4940,39 +5076,175 @@
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>other-contact</t>
+          <t>contact-reference</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>Other site visit contact</t>
-        </is>
-      </c>
-      <c r="F91" s="2" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="G91" s="2" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
+          <t>Contact reference</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr"/>
+      <c r="G91" s="2" t="inlineStr"/>
       <c r="H91" s="2" t="inlineStr"/>
       <c r="I91" s="2" t="inlineStr"/>
       <c r="J91" s="2" t="inlineStr"/>
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr">
         <is>
+          <t>The reference of the applicant or agent who should be contacted for site visits</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>MAY</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="n"/>
+      <c r="B92" s="2" t="n"/>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>Information to help the planning authority arrange a site visit</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>other-contact</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>Other site visit contact</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>fullname</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>Full name</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr"/>
+      <c r="I92" s="2" t="inlineStr"/>
+      <c r="J92" s="2" t="inlineStr"/>
+      <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>The complete name of a person</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="n"/>
+      <c r="B93" s="2" t="n"/>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>Information to help the planning authority arrange a site visit</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>other-contact</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>Other site visit contact</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>Phone number</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr"/>
+      <c r="I93" s="2" t="inlineStr"/>
+      <c r="J93" s="2" t="inlineStr"/>
+      <c r="K93" s="2" t="inlineStr"/>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>A phone number</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="n"/>
+      <c r="B94" s="2" t="n"/>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>Information to help the planning authority arrange a site visit</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>other-contact</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>Other site visit contact</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr"/>
+      <c r="I94" s="2" t="inlineStr"/>
+      <c r="J94" s="2" t="inlineStr"/>
+      <c r="K94" s="2" t="inlineStr"/>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
           <t>The email address that can be used for electronic correspondence with the individual</t>
         </is>
       </c>
-      <c r="M91" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="N91" s="2" t="inlineStr">
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N94" s="2" t="inlineStr">
         <is>
           <t>MUST</t>
         </is>
@@ -4980,34 +5252,34 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="A43"/>
+    <mergeCell ref="A80:A88"/>
+    <mergeCell ref="B51:B58"/>
+    <mergeCell ref="A37:A43"/>
+    <mergeCell ref="B46:B47"/>
     <mergeCell ref="A2:A19"/>
-    <mergeCell ref="A24:A31"/>
-    <mergeCell ref="A49:A56"/>
-    <mergeCell ref="A36:A41"/>
-    <mergeCell ref="A72:A76"/>
-    <mergeCell ref="B57:B71"/>
-    <mergeCell ref="B86:B91"/>
-    <mergeCell ref="B72:B76"/>
-    <mergeCell ref="B44:B45"/>
-    <mergeCell ref="A32:A35"/>
-    <mergeCell ref="B43"/>
-    <mergeCell ref="A57:A71"/>
-    <mergeCell ref="A86:A91"/>
+    <mergeCell ref="A51:A58"/>
+    <mergeCell ref="A44"/>
+    <mergeCell ref="B37:B43"/>
+    <mergeCell ref="B45"/>
+    <mergeCell ref="A46:A47"/>
+    <mergeCell ref="B24:B32"/>
+    <mergeCell ref="A59:A74"/>
+    <mergeCell ref="A33:A36"/>
+    <mergeCell ref="B80:B88"/>
+    <mergeCell ref="A45"/>
+    <mergeCell ref="A89:A94"/>
+    <mergeCell ref="A48:A50"/>
     <mergeCell ref="A20:A23"/>
-    <mergeCell ref="A77:A85"/>
-    <mergeCell ref="B46:B48"/>
-    <mergeCell ref="B42"/>
-    <mergeCell ref="A44:A45"/>
-    <mergeCell ref="B36:B41"/>
-    <mergeCell ref="B49:B56"/>
+    <mergeCell ref="B59:B74"/>
+    <mergeCell ref="B33:B36"/>
+    <mergeCell ref="B75:B79"/>
+    <mergeCell ref="B89:B94"/>
+    <mergeCell ref="A24:A32"/>
+    <mergeCell ref="B44"/>
+    <mergeCell ref="B48:B50"/>
     <mergeCell ref="B20:B23"/>
     <mergeCell ref="B2:B19"/>
-    <mergeCell ref="B24:B31"/>
-    <mergeCell ref="A42"/>
-    <mergeCell ref="A46:A48"/>
-    <mergeCell ref="B77:B85"/>
-    <mergeCell ref="B32:B35"/>
+    <mergeCell ref="A75:A79"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
